--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987125</v>
+        <v>124983563</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587084</v>
+        <v>586799</v>
       </c>
       <c r="R2" t="n">
-        <v>6938203</v>
+        <v>6938055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124984652</v>
+        <v>124983267</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -823,14 +833,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586891</v>
+        <v>586804</v>
       </c>
       <c r="R3" t="n">
-        <v>6937995</v>
+        <v>6938078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124982589</v>
+        <v>124988185</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586904</v>
+        <v>587197</v>
       </c>
       <c r="R4" t="n">
-        <v>6938096</v>
+        <v>6938055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987424</v>
+        <v>124988323</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587103</v>
+        <v>587174</v>
       </c>
       <c r="R5" t="n">
-        <v>6938206</v>
+        <v>6938028</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124989520</v>
+        <v>124982289</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1159,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587123</v>
+        <v>586956</v>
       </c>
       <c r="R6" t="n">
-        <v>6937980</v>
+        <v>6938114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124982567</v>
+        <v>124988914</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1281,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586907</v>
+        <v>587193</v>
       </c>
       <c r="R7" t="n">
-        <v>6938087</v>
+        <v>6937956</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1375,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124988491</v>
+        <v>124987889</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,43 +1403,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587193</v>
+        <v>587214</v>
       </c>
       <c r="R8" t="n">
-        <v>6938003</v>
+        <v>6938134</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,7 +1499,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124986178</v>
+        <v>124989520</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1513,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587008</v>
+        <v>587123</v>
       </c>
       <c r="R9" t="n">
-        <v>6938211</v>
+        <v>6937980</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124986659</v>
+        <v>124986503</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,37 +1627,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587032</v>
+        <v>587003</v>
       </c>
       <c r="R10" t="n">
-        <v>6938236</v>
+        <v>6938230</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,22 +1721,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987817</v>
+        <v>124981850</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,25 +1745,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587218</v>
+        <v>587051</v>
       </c>
       <c r="R11" t="n">
-        <v>6938125</v>
+        <v>6938101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124989421</v>
+        <v>124981756</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,37 +1861,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587147</v>
+        <v>587045</v>
       </c>
       <c r="R12" t="n">
-        <v>6937978</v>
+        <v>6938068</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1935,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,22 +1955,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124988918</v>
+        <v>124986538</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,39 +1983,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587221</v>
+        <v>587003</v>
       </c>
       <c r="R13" t="n">
-        <v>6937950</v>
+        <v>6938235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2042,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,12 +2052,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,19 +2067,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988914</v>
+        <v>124988969</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2079,7 +2115,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2088,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587193</v>
+        <v>587225</v>
       </c>
       <c r="R14" t="n">
-        <v>6937956</v>
+        <v>6937951</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2153,22 +2189,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124982289</v>
+        <v>124982567</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,39 +2217,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586956</v>
+        <v>586907</v>
       </c>
       <c r="R15" t="n">
-        <v>6938114</v>
+        <v>6938087</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,12 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,22 +2301,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124981756</v>
+        <v>124988050</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,42 +2329,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587045</v>
+        <v>587221</v>
       </c>
       <c r="R16" t="n">
-        <v>6938068</v>
+        <v>6938107</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,7 +2388,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,12 +2398,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2413,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124985568</v>
+        <v>124989421</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,39 +2441,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587027</v>
+        <v>587147</v>
       </c>
       <c r="R17" t="n">
-        <v>6938028</v>
+        <v>6937978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,12 +2510,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,22 +2525,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124985796</v>
+        <v>124990166</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,38 +2549,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587080</v>
+        <v>587097</v>
       </c>
       <c r="R18" t="n">
-        <v>6938107</v>
+        <v>6937989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,22 +2646,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124988270</v>
+        <v>124982787</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,34 +2674,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587190</v>
+        <v>586882</v>
       </c>
       <c r="R19" t="n">
-        <v>6938036</v>
+        <v>6938074</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2748,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,22 +2768,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124982170</v>
+        <v>124988529</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,39 +2796,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586964</v>
+        <v>587145</v>
       </c>
       <c r="R20" t="n">
-        <v>6938109</v>
+        <v>6938003</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,12 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,19 +2880,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124986503</v>
+        <v>124981283</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2911,29 +2926,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587003</v>
+        <v>587053</v>
       </c>
       <c r="R21" t="n">
-        <v>6938230</v>
+        <v>6938038</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2982,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,19 +3002,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124988641</v>
+        <v>124988918</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3044,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587123</v>
+        <v>587221</v>
       </c>
       <c r="R22" t="n">
-        <v>6937990</v>
+        <v>6937950</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3079,7 +3094,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3104,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3121,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124982003</v>
+        <v>124986918</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,21 +3152,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3161,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587036</v>
+        <v>587054</v>
       </c>
       <c r="R23" t="n">
-        <v>6938128</v>
+        <v>6938245</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,7 +3211,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3221,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3248,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124981403</v>
+        <v>124982589</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,39 +3264,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587070</v>
+        <v>586904</v>
       </c>
       <c r="R24" t="n">
-        <v>6938040</v>
+        <v>6938096</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3313,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,12 +3333,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3355,10 +3360,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124983267</v>
+        <v>124989553</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3367,38 +3372,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586804</v>
+        <v>587128</v>
       </c>
       <c r="R25" t="n">
-        <v>6938078</v>
+        <v>6937990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3430,7 +3444,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,7 +3454,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,10 +3481,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124988185</v>
+        <v>124983653</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3483,34 +3497,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587197</v>
+        <v>586814</v>
       </c>
       <c r="R26" t="n">
-        <v>6938055</v>
+        <v>6938043</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3542,7 +3561,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3552,7 +3571,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3567,22 +3591,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124981660</v>
+        <v>124986659</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,21 +3619,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3643,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587048</v>
+        <v>587032</v>
       </c>
       <c r="R27" t="n">
-        <v>6938056</v>
+        <v>6938236</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3654,7 +3678,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3664,7 +3688,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3691,10 +3715,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124981283</v>
+        <v>124987318</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,39 +3731,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587053</v>
+        <v>587102</v>
       </c>
       <c r="R28" t="n">
-        <v>6938038</v>
+        <v>6938235</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3771,7 +3790,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3781,12 +3800,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,10 +3827,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124982787</v>
+        <v>124981815</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,43 +3839,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586882</v>
+        <v>587032</v>
       </c>
       <c r="R29" t="n">
-        <v>6938074</v>
+        <v>6938083</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3893,7 +3906,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3903,12 +3916,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,19 +3931,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124983563</v>
+        <v>124982170</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3971,7 +3979,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3980,10 +3988,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586799</v>
+        <v>586964</v>
       </c>
       <c r="R30" t="n">
-        <v>6938055</v>
+        <v>6938109</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4015,7 +4023,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4025,7 +4033,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4045,22 +4053,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124985931</v>
+        <v>124982748</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4073,39 +4081,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587058</v>
+        <v>586911</v>
       </c>
       <c r="R31" t="n">
-        <v>6938138</v>
+        <v>6938088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4137,7 +4140,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4147,12 +4150,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4179,10 +4177,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124987740</v>
+        <v>124984652</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4195,34 +4193,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587191</v>
+        <v>586891</v>
       </c>
       <c r="R32" t="n">
-        <v>6938140</v>
+        <v>6937995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,7 +4252,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4264,7 +4262,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4291,10 +4289,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124981850</v>
+        <v>124981684</v>
       </c>
       <c r="B33" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4303,38 +4301,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587051</v>
+        <v>587057</v>
       </c>
       <c r="R33" t="n">
-        <v>6938101</v>
+        <v>6938054</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4366,7 +4368,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4376,7 +4378,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,10 +4405,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124983653</v>
+        <v>124987383</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4419,39 +4421,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586814</v>
+        <v>587108</v>
       </c>
       <c r="R34" t="n">
-        <v>6938043</v>
+        <v>6938215</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4483,7 +4480,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4493,12 +4490,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4513,22 +4505,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124987521</v>
+        <v>124987817</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4541,21 +4533,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4565,10 +4557,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587127</v>
+        <v>587218</v>
       </c>
       <c r="R35" t="n">
-        <v>6938166</v>
+        <v>6938125</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4600,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4610,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4749,10 +4741,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124987066</v>
+        <v>124983114</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4765,34 +4757,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587081</v>
+        <v>586836</v>
       </c>
       <c r="R37" t="n">
-        <v>6938219</v>
+        <v>6938079</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4824,7 +4816,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4834,7 +4826,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4849,22 +4841,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124987383</v>
+        <v>124987424</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4877,34 +4869,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587108</v>
+        <v>587103</v>
       </c>
       <c r="R38" t="n">
-        <v>6938215</v>
+        <v>6938206</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4936,7 +4933,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4946,7 +4943,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4961,22 +4958,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124988529</v>
+        <v>124985796</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4989,21 +4986,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5013,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587145</v>
+        <v>587080</v>
       </c>
       <c r="R39" t="n">
-        <v>6938003</v>
+        <v>6938107</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5048,7 +5045,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5058,7 +5055,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5085,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124987318</v>
+        <v>124985568</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5101,34 +5098,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587102</v>
+        <v>587027</v>
       </c>
       <c r="R40" t="n">
-        <v>6938235</v>
+        <v>6938028</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5160,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5170,7 +5172,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5185,22 +5192,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124981684</v>
+        <v>124985931</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5209,30 +5216,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5241,10 +5249,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587057</v>
+        <v>587058</v>
       </c>
       <c r="R41" t="n">
-        <v>6938054</v>
+        <v>6938138</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5276,7 +5284,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5286,7 +5294,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5313,10 +5326,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124981815</v>
+        <v>124988270</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5325,42 +5338,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587032</v>
+        <v>587190</v>
       </c>
       <c r="R42" t="n">
-        <v>6938083</v>
+        <v>6938036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5392,7 +5401,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5402,7 +5411,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5429,10 +5438,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124988969</v>
+        <v>124987066</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5445,39 +5454,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587225</v>
+        <v>587081</v>
       </c>
       <c r="R43" t="n">
-        <v>6937951</v>
+        <v>6938219</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5509,7 +5513,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5519,12 +5523,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5539,22 +5538,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124990166</v>
+        <v>124982003</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5563,47 +5562,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587097</v>
+        <v>587036</v>
       </c>
       <c r="R44" t="n">
-        <v>6937989</v>
+        <v>6938128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5635,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5645,7 +5635,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5660,22 +5650,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124986538</v>
+        <v>124988641</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5688,34 +5678,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587003</v>
+        <v>587123</v>
       </c>
       <c r="R45" t="n">
-        <v>6938235</v>
+        <v>6937990</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5747,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5757,7 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5772,22 +5772,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124986918</v>
+        <v>124981660</v>
       </c>
       <c r="B46" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5800,21 +5800,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587054</v>
+        <v>587048</v>
       </c>
       <c r="R46" t="n">
-        <v>6938245</v>
+        <v>6938056</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5896,10 +5896,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124983114</v>
+        <v>124987125</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5912,34 +5912,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586836</v>
+        <v>587084</v>
       </c>
       <c r="R47" t="n">
-        <v>6938079</v>
+        <v>6938203</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6008,10 +6008,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124982748</v>
+        <v>124988491</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6020,38 +6020,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586911</v>
+        <v>587193</v>
       </c>
       <c r="R48" t="n">
-        <v>6938088</v>
+        <v>6938003</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6083,7 +6092,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6093,7 +6102,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6108,22 +6117,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124988323</v>
+        <v>124987521</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6136,39 +6145,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587174</v>
+        <v>587127</v>
       </c>
       <c r="R49" t="n">
-        <v>6938028</v>
+        <v>6938166</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6200,7 +6204,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,12 +6214,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6242,10 +6241,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124989553</v>
+        <v>124987740</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6254,47 +6253,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587128</v>
+        <v>587191</v>
       </c>
       <c r="R50" t="n">
-        <v>6937990</v>
+        <v>6938140</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6326,7 +6316,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6336,7 +6326,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6351,22 +6341,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124987889</v>
+        <v>124981403</v>
       </c>
       <c r="B51" t="n">
-        <v>91457</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6375,38 +6365,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587214</v>
+        <v>587070</v>
       </c>
       <c r="R51" t="n">
-        <v>6938134</v>
+        <v>6938040</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6438,7 +6433,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6448,7 +6443,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6475,7 +6475,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124988050</v>
+        <v>124986178</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587221</v>
+        <v>587008</v>
       </c>
       <c r="R52" t="n">
-        <v>6938107</v>
+        <v>6938211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124983563</v>
+        <v>124987521</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586799</v>
+        <v>587127</v>
       </c>
       <c r="R2" t="n">
-        <v>6938055</v>
+        <v>6938166</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124983267</v>
+        <v>124987383</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586804</v>
+        <v>587108</v>
       </c>
       <c r="R3" t="n">
-        <v>6938078</v>
+        <v>6938215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124988185</v>
+        <v>124988323</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587197</v>
+        <v>587174</v>
       </c>
       <c r="R4" t="n">
-        <v>6938055</v>
+        <v>6938028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988323</v>
+        <v>124988491</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1033,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587174</v>
+        <v>587193</v>
       </c>
       <c r="R5" t="n">
-        <v>6938028</v>
+        <v>6938003</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124982289</v>
+        <v>124989421</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,39 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586956</v>
+        <v>587147</v>
       </c>
       <c r="R6" t="n">
-        <v>6938114</v>
+        <v>6937978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988914</v>
+        <v>124990166</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,31 +1266,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587193</v>
+        <v>587097</v>
       </c>
       <c r="R7" t="n">
-        <v>6937956</v>
+        <v>6937989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987889</v>
+        <v>124988185</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,25 +1387,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587214</v>
+        <v>587197</v>
       </c>
       <c r="R8" t="n">
-        <v>6938134</v>
+        <v>6938055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,22 +1475,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124989520</v>
+        <v>124982589</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,34 +1503,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587123</v>
+        <v>586904</v>
       </c>
       <c r="R9" t="n">
-        <v>6937980</v>
+        <v>6938096</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,19 +1587,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124986503</v>
+        <v>124982170</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1645,14 +1633,9 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1661,13 +1644,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587003</v>
+        <v>586964</v>
       </c>
       <c r="R10" t="n">
-        <v>6938230</v>
+        <v>6938109</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124981850</v>
+        <v>124983114</v>
       </c>
       <c r="B11" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,38 +1733,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587051</v>
+        <v>586836</v>
       </c>
       <c r="R11" t="n">
-        <v>6938101</v>
+        <v>6938079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124981756</v>
+        <v>124982003</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,42 +1849,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587045</v>
+        <v>587036</v>
       </c>
       <c r="R12" t="n">
-        <v>6938068</v>
+        <v>6938128</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,12 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,22 +1933,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124986538</v>
+        <v>124982748</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,21 +1961,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2007,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587003</v>
+        <v>586911</v>
       </c>
       <c r="R13" t="n">
-        <v>6938235</v>
+        <v>6938088</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2052,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,19 +2045,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988969</v>
+        <v>124988914</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2115,7 +2093,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2124,10 +2102,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587225</v>
+        <v>587193</v>
       </c>
       <c r="R14" t="n">
-        <v>6937951</v>
+        <v>6937956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2189,22 +2167,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124982567</v>
+        <v>124981403</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,34 +2195,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586907</v>
+        <v>587070</v>
       </c>
       <c r="R15" t="n">
-        <v>6938087</v>
+        <v>6938040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2269,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,22 +2289,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124988050</v>
+        <v>124983563</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,34 +2317,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587221</v>
+        <v>586799</v>
       </c>
       <c r="R16" t="n">
-        <v>6938107</v>
+        <v>6938055</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,7 +2391,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124989421</v>
+        <v>124988641</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,34 +2439,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587147</v>
+        <v>587123</v>
       </c>
       <c r="R17" t="n">
-        <v>6937978</v>
+        <v>6937990</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,7 +2503,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2513,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124990166</v>
+        <v>124984652</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2549,47 +2557,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587097</v>
+        <v>586891</v>
       </c>
       <c r="R18" t="n">
-        <v>6937989</v>
+        <v>6937995</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2620,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,7 +2630,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,22 +2645,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124982787</v>
+        <v>124981850</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2670,43 +2669,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586882</v>
+        <v>587051</v>
       </c>
       <c r="R19" t="n">
-        <v>6938074</v>
+        <v>6938101</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,7 +2732,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,12 +2742,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,22 +2757,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124988529</v>
+        <v>124986538</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,34 +2785,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587145</v>
+        <v>587003</v>
       </c>
       <c r="R20" t="n">
-        <v>6938003</v>
+        <v>6938235</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2855,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,22 +2869,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124981283</v>
+        <v>124988270</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,39 +2897,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587053</v>
+        <v>587190</v>
       </c>
       <c r="R21" t="n">
-        <v>6938038</v>
+        <v>6938036</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,7 +2956,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,12 +2966,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124988918</v>
+        <v>124982567</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,39 +3009,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587221</v>
+        <v>586907</v>
       </c>
       <c r="R22" t="n">
-        <v>6937950</v>
+        <v>6938087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,7 +3068,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3104,12 +3078,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,10 +3105,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124986918</v>
+        <v>124986503</v>
       </c>
       <c r="B23" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3152,37 +3121,47 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587054</v>
+        <v>587003</v>
       </c>
       <c r="R23" t="n">
-        <v>6938245</v>
+        <v>6938230</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3211,7 +3190,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3221,7 +3200,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,22 +3215,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124982589</v>
+        <v>124987318</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3264,34 +3243,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586904</v>
+        <v>587102</v>
       </c>
       <c r="R24" t="n">
-        <v>6938096</v>
+        <v>6938235</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,7 +3302,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3333,7 +3312,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,22 +3327,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124989553</v>
+        <v>124986659</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3372,47 +3351,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587128</v>
+        <v>587032</v>
       </c>
       <c r="R25" t="n">
-        <v>6937990</v>
+        <v>6938236</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3444,7 +3414,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3454,7 +3424,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3469,22 +3439,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124983653</v>
+        <v>124981815</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3493,43 +3463,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586814</v>
+        <v>587032</v>
       </c>
       <c r="R26" t="n">
-        <v>6938043</v>
+        <v>6938083</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3561,7 +3530,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3571,12 +3540,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,22 +3555,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124986659</v>
+        <v>124988529</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3619,21 +3583,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3643,10 +3607,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587032</v>
+        <v>587145</v>
       </c>
       <c r="R27" t="n">
-        <v>6938236</v>
+        <v>6938003</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3678,7 +3642,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3688,7 +3652,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3715,10 +3679,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124987318</v>
+        <v>124982289</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3731,34 +3695,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587102</v>
+        <v>586956</v>
       </c>
       <c r="R28" t="n">
-        <v>6938235</v>
+        <v>6938114</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3800,7 +3769,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3815,22 +3789,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124981815</v>
+        <v>124988918</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3839,30 +3813,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3871,10 +3846,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587032</v>
+        <v>587221</v>
       </c>
       <c r="R29" t="n">
-        <v>6938083</v>
+        <v>6937950</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3906,7 +3881,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3916,7 +3891,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3943,10 +3923,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124982170</v>
+        <v>124981660</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3959,39 +3939,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586964</v>
+        <v>587048</v>
       </c>
       <c r="R30" t="n">
-        <v>6938109</v>
+        <v>6938056</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4023,7 +3998,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4033,12 +4008,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4053,22 +4023,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124982748</v>
+        <v>124985931</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4081,34 +4051,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586911</v>
+        <v>587058</v>
       </c>
       <c r="R31" t="n">
-        <v>6938088</v>
+        <v>6938138</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4140,7 +4115,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4150,7 +4125,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4177,10 +4157,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124984652</v>
+        <v>124987740</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4193,34 +4173,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586891</v>
+        <v>587191</v>
       </c>
       <c r="R32" t="n">
-        <v>6937995</v>
+        <v>6938140</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4252,7 +4232,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4262,7 +4242,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4289,10 +4269,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124981684</v>
+        <v>124983653</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4301,42 +4281,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587057</v>
+        <v>586814</v>
       </c>
       <c r="R33" t="n">
-        <v>6938054</v>
+        <v>6938043</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4368,7 +4349,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4378,7 +4359,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4393,22 +4379,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124987383</v>
+        <v>124988969</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4421,34 +4407,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587108</v>
+        <v>587225</v>
       </c>
       <c r="R34" t="n">
-        <v>6938215</v>
+        <v>6937951</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4480,7 +4471,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4481,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,10 +4513,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124987817</v>
+        <v>124985796</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4533,21 +4529,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4557,10 +4553,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587218</v>
+        <v>587080</v>
       </c>
       <c r="R35" t="n">
-        <v>6938125</v>
+        <v>6938107</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4592,7 +4588,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4598,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,10 +4625,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124988415</v>
+        <v>124987066</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4645,21 +4641,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4669,10 +4665,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587161</v>
+        <v>587081</v>
       </c>
       <c r="R36" t="n">
-        <v>6938018</v>
+        <v>6938219</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4704,7 +4700,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4714,7 +4710,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4729,22 +4725,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124983114</v>
+        <v>124989553</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4753,38 +4749,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586836</v>
+        <v>587128</v>
       </c>
       <c r="R37" t="n">
-        <v>6938079</v>
+        <v>6937990</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4816,7 +4821,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4826,7 +4831,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4841,12 +4846,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4970,10 +4975,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124985796</v>
+        <v>124989520</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4986,21 +4991,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5010,10 +5015,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587080</v>
+        <v>587123</v>
       </c>
       <c r="R39" t="n">
-        <v>6938107</v>
+        <v>6937980</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5045,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5055,7 +5060,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5082,7 +5087,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124985568</v>
+        <v>124981283</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5123,14 +5128,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587027</v>
+        <v>587053</v>
       </c>
       <c r="R40" t="n">
-        <v>6938028</v>
+        <v>6938038</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5172,12 +5177,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,22 +5197,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124985931</v>
+        <v>124986918</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5220,39 +5225,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587058</v>
+        <v>587054</v>
       </c>
       <c r="R41" t="n">
-        <v>6938138</v>
+        <v>6938245</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5294,12 +5294,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5326,7 +5321,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124988270</v>
+        <v>124983267</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5362,14 +5357,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587190</v>
+        <v>586804</v>
       </c>
       <c r="R42" t="n">
-        <v>6938036</v>
+        <v>6938078</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5401,7 +5396,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5411,7 +5406,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5426,22 +5421,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124987066</v>
+        <v>124988415</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5454,21 +5449,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5478,10 +5473,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587081</v>
+        <v>587161</v>
       </c>
       <c r="R43" t="n">
-        <v>6938219</v>
+        <v>6938018</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5513,7 +5508,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5523,7 +5518,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5538,22 +5533,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124982003</v>
+        <v>124985568</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5566,34 +5561,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587036</v>
+        <v>587027</v>
       </c>
       <c r="R44" t="n">
-        <v>6938128</v>
+        <v>6938028</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,7 +5635,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5650,22 +5655,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124988641</v>
+        <v>124987889</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5674,43 +5679,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587123</v>
+        <v>587214</v>
       </c>
       <c r="R45" t="n">
-        <v>6937990</v>
+        <v>6938134</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5752,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5772,22 +5767,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124981660</v>
+        <v>124981756</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5800,37 +5795,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587048</v>
+        <v>587045</v>
       </c>
       <c r="R46" t="n">
-        <v>6938056</v>
+        <v>6938068</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5869,7 +5869,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5884,12 +5889,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6008,10 +6013,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124988491</v>
+        <v>124987817</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6020,47 +6025,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587193</v>
+        <v>587218</v>
       </c>
       <c r="R48" t="n">
-        <v>6938003</v>
+        <v>6938125</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6092,7 +6088,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6102,7 +6098,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6117,22 +6113,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124987521</v>
+        <v>124988050</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6145,21 +6141,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6169,10 +6165,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587127</v>
+        <v>587221</v>
       </c>
       <c r="R49" t="n">
-        <v>6938166</v>
+        <v>6938107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6204,7 +6200,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6214,7 +6210,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6241,10 +6237,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124987740</v>
+        <v>124982787</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6257,34 +6253,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587191</v>
+        <v>586882</v>
       </c>
       <c r="R50" t="n">
-        <v>6938140</v>
+        <v>6938074</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6316,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6326,7 +6327,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6341,22 +6347,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124981403</v>
+        <v>124981684</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6365,31 +6371,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6398,10 +6403,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587070</v>
+        <v>587057</v>
       </c>
       <c r="R51" t="n">
-        <v>6938040</v>
+        <v>6938054</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,7 +6438,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6443,12 +6448,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6463,12 +6463,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987521</v>
+        <v>124987383</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587127</v>
+        <v>587108</v>
       </c>
       <c r="R2" t="n">
-        <v>6938166</v>
+        <v>6938215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987383</v>
+        <v>124987521</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587108</v>
+        <v>587127</v>
       </c>
       <c r="R3" t="n">
-        <v>6938215</v>
+        <v>6938166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988491</v>
+        <v>124989421</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,47 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587193</v>
+        <v>587147</v>
       </c>
       <c r="R5" t="n">
-        <v>6938003</v>
+        <v>6937978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124989421</v>
+        <v>124990166</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1145,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587147</v>
+        <v>587097</v>
       </c>
       <c r="R6" t="n">
-        <v>6937978</v>
+        <v>6937989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,19 +1242,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124990166</v>
+        <v>124988491</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587097</v>
+        <v>587193</v>
       </c>
       <c r="R7" t="n">
-        <v>6937989</v>
+        <v>6938003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124988185</v>
+        <v>124982589</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587197</v>
+        <v>586904</v>
       </c>
       <c r="R8" t="n">
-        <v>6938055</v>
+        <v>6938096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,22 +1475,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124982589</v>
+        <v>124988185</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,34 +1503,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586904</v>
+        <v>587197</v>
       </c>
       <c r="R9" t="n">
-        <v>6938096</v>
+        <v>6938055</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,12 +1587,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124986538</v>
+        <v>124982567</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587003</v>
+        <v>586907</v>
       </c>
       <c r="R20" t="n">
-        <v>6938235</v>
+        <v>6938087</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,19 +2869,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124988270</v>
+        <v>124988529</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2921,10 +2921,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587190</v>
+        <v>587145</v>
       </c>
       <c r="R21" t="n">
-        <v>6938036</v>
+        <v>6938003</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124982567</v>
+        <v>124986659</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,34 +3009,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586907</v>
+        <v>587032</v>
       </c>
       <c r="R22" t="n">
-        <v>6938087</v>
+        <v>6938236</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124986503</v>
+        <v>124981815</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,51 +3117,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587003</v>
+        <v>587032</v>
       </c>
       <c r="R23" t="n">
-        <v>6938230</v>
+        <v>6938083</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3190,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3200,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3215,19 +3209,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124987318</v>
+        <v>124986538</v>
       </c>
       <c r="B24" t="n">
         <v>79891</v>
@@ -3263,11 +3257,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587102</v>
+        <v>587003</v>
       </c>
       <c r="R24" t="n">
         <v>6938235</v>
@@ -3302,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3312,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,22 +3321,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124986659</v>
+        <v>124988270</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3355,21 +3349,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3379,10 +3373,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587032</v>
+        <v>587190</v>
       </c>
       <c r="R25" t="n">
-        <v>6938236</v>
+        <v>6938036</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3414,7 +3408,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3424,7 +3418,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3451,10 +3445,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124981815</v>
+        <v>124986503</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,45 +3457,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587032</v>
+        <v>587003</v>
       </c>
       <c r="R26" t="n">
-        <v>6938083</v>
+        <v>6938230</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3555,22 +3555,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124988529</v>
+        <v>124987318</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,21 +3583,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587145</v>
+        <v>587102</v>
       </c>
       <c r="R27" t="n">
-        <v>6938003</v>
+        <v>6938235</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4269,7 +4269,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124983653</v>
+        <v>124988969</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4305,19 +4305,19 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586814</v>
+        <v>587225</v>
       </c>
       <c r="R33" t="n">
-        <v>6938043</v>
+        <v>6937951</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4379,22 +4379,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124988969</v>
+        <v>124985796</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,39 +4407,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587225</v>
+        <v>587080</v>
       </c>
       <c r="R34" t="n">
-        <v>6937951</v>
+        <v>6938107</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4471,7 +4466,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4481,12 +4476,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4513,10 +4503,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124985796</v>
+        <v>124983653</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4529,34 +4519,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587080</v>
+        <v>586814</v>
       </c>
       <c r="R35" t="n">
-        <v>6938107</v>
+        <v>6938043</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4588,7 +4583,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4598,7 +4593,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4613,12 +4613,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124989520</v>
+        <v>124981283</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4991,34 +4991,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587123</v>
+        <v>587053</v>
       </c>
       <c r="R39" t="n">
-        <v>6937980</v>
+        <v>6938038</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5050,7 +5055,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5060,7 +5065,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5087,10 +5097,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124981283</v>
+        <v>124989520</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,39 +5113,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587053</v>
+        <v>587123</v>
       </c>
       <c r="R40" t="n">
-        <v>6938038</v>
+        <v>6937980</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5167,7 +5172,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5177,12 +5182,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5209,10 +5209,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124986918</v>
+        <v>124983267</v>
       </c>
       <c r="B41" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5225,34 +5225,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587054</v>
+        <v>586804</v>
       </c>
       <c r="R41" t="n">
-        <v>6938245</v>
+        <v>6938078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5309,22 +5309,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124983267</v>
+        <v>124985568</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5337,34 +5337,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586804</v>
+        <v>587027</v>
       </c>
       <c r="R42" t="n">
-        <v>6938078</v>
+        <v>6938028</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5396,7 +5401,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5406,7 +5411,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5545,10 +5555,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124985568</v>
+        <v>124986918</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5561,39 +5571,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587027</v>
+        <v>587054</v>
       </c>
       <c r="R44" t="n">
-        <v>6938028</v>
+        <v>6938245</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5625,7 +5630,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5635,12 +5640,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5655,12 +5655,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987383</v>
+        <v>124989553</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587108</v>
+        <v>587128</v>
       </c>
       <c r="R2" t="n">
-        <v>6938215</v>
+        <v>6937990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987521</v>
+        <v>124986659</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587127</v>
+        <v>587032</v>
       </c>
       <c r="R3" t="n">
-        <v>6938166</v>
+        <v>6938236</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124988323</v>
+        <v>124986538</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +924,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587174</v>
+        <v>587003</v>
       </c>
       <c r="R4" t="n">
-        <v>6938028</v>
+        <v>6938235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,19 +1008,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124989421</v>
+        <v>124981660</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1061,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587147</v>
+        <v>587048</v>
       </c>
       <c r="R5" t="n">
-        <v>6937978</v>
+        <v>6938056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124990166</v>
+        <v>124987318</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,47 +1144,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587097</v>
+        <v>587102</v>
       </c>
       <c r="R6" t="n">
-        <v>6937989</v>
+        <v>6938235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,19 +1232,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988491</v>
+        <v>124981815</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1289,12 +1279,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1303,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587193</v>
+        <v>587032</v>
       </c>
       <c r="R7" t="n">
-        <v>6938003</v>
+        <v>6938083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1348,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124982589</v>
+        <v>124982787</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1376,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586904</v>
+        <v>586882</v>
       </c>
       <c r="R8" t="n">
-        <v>6938096</v>
+        <v>6938074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124988185</v>
+        <v>124986918</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587197</v>
+        <v>587054</v>
       </c>
       <c r="R9" t="n">
-        <v>6938055</v>
+        <v>6938245</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124982170</v>
+        <v>124988415</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,39 +1610,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586964</v>
+        <v>587161</v>
       </c>
       <c r="R10" t="n">
-        <v>6938109</v>
+        <v>6938018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,22 +1694,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124983114</v>
+        <v>124988969</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,34 +1722,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586836</v>
+        <v>587225</v>
       </c>
       <c r="R11" t="n">
-        <v>6938079</v>
+        <v>6937951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1796,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124982003</v>
+        <v>124987889</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>91457</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,25 +1840,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587036</v>
+        <v>587214</v>
       </c>
       <c r="R12" t="n">
-        <v>6938128</v>
+        <v>6938134</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,22 +1928,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124982748</v>
+        <v>124981850</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,38 +1952,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586911</v>
+        <v>587051</v>
       </c>
       <c r="R13" t="n">
-        <v>6938088</v>
+        <v>6938101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,7 +2052,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988914</v>
+        <v>124982170</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2093,19 +2088,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587193</v>
+        <v>586964</v>
       </c>
       <c r="R14" t="n">
-        <v>6937956</v>
+        <v>6938109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2301,10 +2296,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124983563</v>
+        <v>124981684</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,43 +2308,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586799</v>
+        <v>587057</v>
       </c>
       <c r="R16" t="n">
-        <v>6938055</v>
+        <v>6938054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,12 +2385,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988641</v>
+        <v>124984652</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2439,39 +2428,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587123</v>
+        <v>586891</v>
       </c>
       <c r="R17" t="n">
-        <v>6937990</v>
+        <v>6937995</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2487,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2513,12 +2497,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124984652</v>
+        <v>124988914</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,34 +2540,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586891</v>
+        <v>587193</v>
       </c>
       <c r="R18" t="n">
-        <v>6937995</v>
+        <v>6937956</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,7 +2604,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2630,7 +2614,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,22 +2634,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124981850</v>
+        <v>124985931</v>
       </c>
       <c r="B19" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2669,38 +2658,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587051</v>
+        <v>587058</v>
       </c>
       <c r="R19" t="n">
-        <v>6938101</v>
+        <v>6938138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2732,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2742,7 +2736,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124982567</v>
+        <v>124989520</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2785,34 +2784,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586907</v>
+        <v>587123</v>
       </c>
       <c r="R20" t="n">
-        <v>6938087</v>
+        <v>6937980</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,7 +2843,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2853,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2881,10 +2880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124988529</v>
+        <v>124987740</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2897,21 +2896,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2921,10 +2920,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587145</v>
+        <v>587191</v>
       </c>
       <c r="R21" t="n">
-        <v>6938003</v>
+        <v>6938140</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2966,7 +2965,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,10 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124986659</v>
+        <v>124988050</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,21 +3008,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3033,10 +3032,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587032</v>
+        <v>587221</v>
       </c>
       <c r="R22" t="n">
-        <v>6938236</v>
+        <v>6938107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,7 +3067,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3078,7 +3077,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3105,10 +3104,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124981815</v>
+        <v>124983563</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,42 +3116,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587032</v>
+        <v>586799</v>
       </c>
       <c r="R23" t="n">
-        <v>6938083</v>
+        <v>6938055</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3194,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,10 +3226,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124986538</v>
+        <v>124982589</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,21 +3242,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,10 +3266,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587003</v>
+        <v>586904</v>
       </c>
       <c r="R24" t="n">
-        <v>6938235</v>
+        <v>6938096</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3301,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3311,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124988270</v>
+        <v>124988491</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3345,38 +3350,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587190</v>
+        <v>587193</v>
       </c>
       <c r="R25" t="n">
-        <v>6938036</v>
+        <v>6938003</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3408,7 +3422,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3418,7 +3432,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,22 +3447,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124986503</v>
+        <v>124987424</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3461,16 +3475,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3479,29 +3493,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587003</v>
+        <v>587103</v>
       </c>
       <c r="R26" t="n">
-        <v>6938230</v>
+        <v>6938206</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3530,7 +3539,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3540,7 +3549,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3567,10 +3576,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124987318</v>
+        <v>124982748</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,34 +3592,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587102</v>
+        <v>586911</v>
       </c>
       <c r="R27" t="n">
-        <v>6938235</v>
+        <v>6938088</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,7 +3651,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3652,7 +3661,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3679,10 +3688,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124982289</v>
+        <v>124986178</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,39 +3704,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586956</v>
+        <v>587008</v>
       </c>
       <c r="R28" t="n">
-        <v>6938114</v>
+        <v>6938211</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,12 +3773,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,22 +3788,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124988918</v>
+        <v>124987817</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3817,39 +3816,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587221</v>
+        <v>587218</v>
       </c>
       <c r="R29" t="n">
-        <v>6937950</v>
+        <v>6938125</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3881,7 +3875,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3891,12 +3885,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124981660</v>
+        <v>124986503</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3939,37 +3928,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587048</v>
+        <v>587003</v>
       </c>
       <c r="R30" t="n">
-        <v>6938056</v>
+        <v>6938230</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3998,7 +3997,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4008,7 +4007,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4023,19 +4022,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124985931</v>
+        <v>124988641</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4071,7 +4070,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4080,10 +4079,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587058</v>
+        <v>587123</v>
       </c>
       <c r="R31" t="n">
-        <v>6938138</v>
+        <v>6937990</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4115,7 +4114,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4125,7 +4124,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4157,10 +4156,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124987740</v>
+        <v>124988918</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4173,34 +4172,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587191</v>
+        <v>587221</v>
       </c>
       <c r="R32" t="n">
-        <v>6938140</v>
+        <v>6937950</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4232,7 +4236,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4242,7 +4246,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4269,10 +4278,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124988969</v>
+        <v>124983114</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4285,39 +4294,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587225</v>
+        <v>586836</v>
       </c>
       <c r="R33" t="n">
-        <v>6937951</v>
+        <v>6938079</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4349,7 +4353,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4359,12 +4363,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4391,10 +4390,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124985796</v>
+        <v>124988270</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,21 +4406,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587080</v>
+        <v>587190</v>
       </c>
       <c r="R34" t="n">
-        <v>6938107</v>
+        <v>6938036</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4466,7 +4465,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4476,7 +4475,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4503,10 +4502,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124983653</v>
+        <v>124987066</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4519,39 +4518,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586814</v>
+        <v>587081</v>
       </c>
       <c r="R35" t="n">
-        <v>6938043</v>
+        <v>6938219</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4583,7 +4577,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4593,12 +4587,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4625,10 +4614,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124987066</v>
+        <v>124988529</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4641,21 +4630,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4665,10 +4654,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587081</v>
+        <v>587145</v>
       </c>
       <c r="R36" t="n">
-        <v>6938219</v>
+        <v>6938003</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4700,7 +4689,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4710,7 +4699,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4725,22 +4714,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124989553</v>
+        <v>124983267</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4749,47 +4738,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587128</v>
+        <v>586804</v>
       </c>
       <c r="R37" t="n">
-        <v>6937990</v>
+        <v>6938078</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4821,7 +4801,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4831,7 +4811,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4858,10 +4838,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124987424</v>
+        <v>124990166</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4870,31 +4850,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4903,10 +4887,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587103</v>
+        <v>587097</v>
       </c>
       <c r="R38" t="n">
-        <v>6938206</v>
+        <v>6937989</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4938,7 +4922,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4948,7 +4932,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4975,10 +4959,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124981283</v>
+        <v>124987383</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4991,39 +4975,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587053</v>
+        <v>587108</v>
       </c>
       <c r="R39" t="n">
-        <v>6938038</v>
+        <v>6938215</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5055,7 +5034,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5065,12 +5044,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5097,10 +5071,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124989520</v>
+        <v>124987521</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5113,21 +5087,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5137,10 +5111,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587123</v>
+        <v>587127</v>
       </c>
       <c r="R40" t="n">
-        <v>6937980</v>
+        <v>6938166</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5172,7 +5146,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5182,7 +5156,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5209,10 +5183,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124983267</v>
+        <v>124985796</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5225,34 +5199,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586804</v>
+        <v>587080</v>
       </c>
       <c r="R41" t="n">
-        <v>6938078</v>
+        <v>6938107</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5284,7 +5258,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5294,7 +5268,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5309,22 +5283,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124985568</v>
+        <v>124989421</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5337,39 +5311,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587027</v>
+        <v>587147</v>
       </c>
       <c r="R42" t="n">
-        <v>6938028</v>
+        <v>6937978</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5401,7 +5370,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5411,12 +5380,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5431,22 +5395,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124988415</v>
+        <v>124981283</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5459,34 +5423,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587161</v>
+        <v>587053</v>
       </c>
       <c r="R43" t="n">
-        <v>6938018</v>
+        <v>6938038</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5518,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5528,7 +5497,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5555,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124986918</v>
+        <v>124981756</v>
       </c>
       <c r="B44" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5571,37 +5545,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587054</v>
+        <v>587045</v>
       </c>
       <c r="R44" t="n">
-        <v>6938245</v>
+        <v>6938068</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5630,7 +5609,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5640,7 +5619,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5655,22 +5639,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124987889</v>
+        <v>124982003</v>
       </c>
       <c r="B45" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5679,25 +5663,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5707,10 +5691,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587214</v>
+        <v>587036</v>
       </c>
       <c r="R45" t="n">
-        <v>6938134</v>
+        <v>6938128</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5742,7 +5726,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,7 +5736,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5767,19 +5751,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124981756</v>
+        <v>124988323</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5815,7 +5799,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5824,13 +5808,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587045</v>
+        <v>587174</v>
       </c>
       <c r="R46" t="n">
-        <v>6938068</v>
+        <v>6938028</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5859,7 +5843,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5869,12 +5853,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5889,12 +5873,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6013,10 +5997,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124987817</v>
+        <v>124985568</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6029,34 +6013,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587218</v>
+        <v>587027</v>
       </c>
       <c r="R48" t="n">
-        <v>6938125</v>
+        <v>6938028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6088,7 +6077,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6098,7 +6087,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6113,19 +6107,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124988050</v>
+        <v>124988185</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -6165,10 +6159,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587221</v>
+        <v>587197</v>
       </c>
       <c r="R49" t="n">
-        <v>6938107</v>
+        <v>6938055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6200,7 +6194,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,7 +6204,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6237,7 +6231,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124982787</v>
+        <v>124983653</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6273,7 +6267,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6282,10 +6276,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586882</v>
+        <v>586814</v>
       </c>
       <c r="R50" t="n">
-        <v>6938074</v>
+        <v>6938043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6317,7 +6311,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6321,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6359,10 +6353,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124981684</v>
+        <v>124982289</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6371,42 +6365,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587057</v>
+        <v>586956</v>
       </c>
       <c r="R51" t="n">
-        <v>6938054</v>
+        <v>6938114</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6438,7 +6433,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6448,7 +6443,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6463,22 +6463,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124986178</v>
+        <v>124982567</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,34 +6491,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587008</v>
+        <v>586907</v>
       </c>
       <c r="R52" t="n">
-        <v>6938211</v>
+        <v>6938087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124989553</v>
+        <v>124986659</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587128</v>
+        <v>587032</v>
       </c>
       <c r="R2" t="n">
-        <v>6937990</v>
+        <v>6938236</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124986659</v>
+        <v>124986538</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -832,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587032</v>
+        <v>587003</v>
       </c>
       <c r="R3" t="n">
-        <v>6938236</v>
+        <v>6938235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124986538</v>
+        <v>124989553</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587003</v>
+        <v>587128</v>
       </c>
       <c r="R4" t="n">
-        <v>6938235</v>
+        <v>6937990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124981850</v>
+        <v>124982170</v>
       </c>
       <c r="B13" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,38 +1952,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587051</v>
+        <v>586964</v>
       </c>
       <c r="R13" t="n">
-        <v>6938101</v>
+        <v>6938109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2030,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,19 +2050,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124982170</v>
+        <v>124981403</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2088,19 +2098,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586964</v>
+        <v>587070</v>
       </c>
       <c r="R14" t="n">
-        <v>6938109</v>
+        <v>6938040</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2174,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124981403</v>
+        <v>124981850</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,43 +2196,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587070</v>
+        <v>587051</v>
       </c>
       <c r="R15" t="n">
-        <v>6938040</v>
+        <v>6938101</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,12 +2269,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,22 +2284,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124981684</v>
+        <v>124984652</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,42 +2308,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587057</v>
+        <v>586891</v>
       </c>
       <c r="R16" t="n">
-        <v>6938054</v>
+        <v>6937995</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2385,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124984652</v>
+        <v>124988914</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,34 +2424,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586891</v>
+        <v>587193</v>
       </c>
       <c r="R17" t="n">
-        <v>6937995</v>
+        <v>6937956</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2497,7 +2498,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,19 +2518,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988914</v>
+        <v>124985931</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2560,7 +2566,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2569,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587193</v>
+        <v>587058</v>
       </c>
       <c r="R18" t="n">
-        <v>6937956</v>
+        <v>6938138</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,7 +2610,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2614,7 +2620,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2634,22 +2640,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124985931</v>
+        <v>124981684</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,31 +2664,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2691,10 +2696,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587058</v>
+        <v>587057</v>
       </c>
       <c r="R19" t="n">
-        <v>6938138</v>
+        <v>6938054</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,12 +2741,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2992,10 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124988050</v>
+        <v>124983563</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3008,34 +3008,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587221</v>
+        <v>586799</v>
       </c>
       <c r="R22" t="n">
-        <v>6938107</v>
+        <v>6938055</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3067,7 +3072,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3077,7 +3082,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3104,10 +3114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124983563</v>
+        <v>124988050</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3120,39 +3130,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586799</v>
+        <v>587221</v>
       </c>
       <c r="R23" t="n">
-        <v>6938055</v>
+        <v>6938107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3189,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,12 +3199,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124988491</v>
+        <v>124982748</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,47 +3350,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587193</v>
+        <v>586911</v>
       </c>
       <c r="R25" t="n">
-        <v>6938003</v>
+        <v>6938088</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3422,7 +3413,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3432,7 +3423,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,22 +3438,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124987424</v>
+        <v>124986178</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3475,39 +3466,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587103</v>
+        <v>587008</v>
       </c>
       <c r="R26" t="n">
-        <v>6938206</v>
+        <v>6938211</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,7 +3525,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3549,7 +3535,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,22 +3550,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124982748</v>
+        <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3592,34 +3578,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586911</v>
+        <v>587103</v>
       </c>
       <c r="R27" t="n">
-        <v>6938088</v>
+        <v>6938206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3651,7 +3642,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3661,7 +3652,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3676,22 +3667,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124986178</v>
+        <v>124988491</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3700,38 +3691,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587008</v>
+        <v>587193</v>
       </c>
       <c r="R28" t="n">
-        <v>6938211</v>
+        <v>6938003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,12 +3788,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124982003</v>
+        <v>124988323</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5667,34 +5667,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587036</v>
+        <v>587174</v>
       </c>
       <c r="R45" t="n">
-        <v>6938128</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5726,7 +5731,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5736,7 +5741,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5763,10 +5773,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124988323</v>
+        <v>124982003</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5779,39 +5789,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587174</v>
+        <v>587036</v>
       </c>
       <c r="R46" t="n">
-        <v>6938028</v>
+        <v>6938128</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5843,7 +5848,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5853,12 +5858,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124986659</v>
+        <v>124987740</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587032</v>
+        <v>587191</v>
       </c>
       <c r="R2" t="n">
-        <v>6938236</v>
+        <v>6938140</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124986538</v>
+        <v>124982567</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587003</v>
+        <v>586907</v>
       </c>
       <c r="R3" t="n">
-        <v>6938235</v>
+        <v>6938087</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124989553</v>
+        <v>124982589</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587128</v>
+        <v>586904</v>
       </c>
       <c r="R4" t="n">
-        <v>6937990</v>
+        <v>6938096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124981660</v>
+        <v>124983653</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587048</v>
+        <v>586814</v>
       </c>
       <c r="R5" t="n">
-        <v>6938056</v>
+        <v>6938043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124987318</v>
+        <v>124983114</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,34 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587102</v>
+        <v>586836</v>
       </c>
       <c r="R6" t="n">
-        <v>6938235</v>
+        <v>6938079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124981815</v>
+        <v>124982170</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,42 +1257,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587032</v>
+        <v>586964</v>
       </c>
       <c r="R7" t="n">
-        <v>6938083</v>
+        <v>6938109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124982787</v>
+        <v>124987889</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,43 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586882</v>
+        <v>587214</v>
       </c>
       <c r="R8" t="n">
-        <v>6938074</v>
+        <v>6938134</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124986918</v>
+        <v>124990166</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,38 +1491,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587054</v>
+        <v>587097</v>
       </c>
       <c r="R9" t="n">
-        <v>6938245</v>
+        <v>6937989</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1588,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124988415</v>
+        <v>124981850</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,25 +1612,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587161</v>
+        <v>587051</v>
       </c>
       <c r="R10" t="n">
-        <v>6938018</v>
+        <v>6938101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124988969</v>
+        <v>124986918</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,39 +1728,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587225</v>
+        <v>587054</v>
       </c>
       <c r="R11" t="n">
-        <v>6937951</v>
+        <v>6938245</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,12 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987889</v>
+        <v>124982289</v>
       </c>
       <c r="B12" t="n">
-        <v>91457</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,38 +1836,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587214</v>
+        <v>586956</v>
       </c>
       <c r="R12" t="n">
-        <v>6938134</v>
+        <v>6938114</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,7 +1946,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124982170</v>
+        <v>124988641</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1976,19 +1982,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586964</v>
+        <v>587123</v>
       </c>
       <c r="R13" t="n">
-        <v>6938109</v>
+        <v>6937990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2050,19 +2056,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124981403</v>
+        <v>124983563</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2103,14 +2109,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587070</v>
+        <v>586799</v>
       </c>
       <c r="R14" t="n">
-        <v>6938040</v>
+        <v>6938055</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2172,22 +2178,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124981850</v>
+        <v>124981756</v>
       </c>
       <c r="B15" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,41 +2202,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587051</v>
+        <v>587045</v>
       </c>
       <c r="R15" t="n">
-        <v>6938101</v>
+        <v>6938068</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2280,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,22 +2300,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124984652</v>
+        <v>124986538</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,34 +2328,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586891</v>
+        <v>587003</v>
       </c>
       <c r="R16" t="n">
-        <v>6937995</v>
+        <v>6938235</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2387,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2397,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,22 +2412,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988914</v>
+        <v>124988185</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,39 +2440,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587193</v>
+        <v>587197</v>
       </c>
       <c r="R17" t="n">
-        <v>6937956</v>
+        <v>6938055</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,12 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,22 +2524,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124985931</v>
+        <v>124983267</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,39 +2552,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587058</v>
+        <v>586804</v>
       </c>
       <c r="R18" t="n">
-        <v>6938138</v>
+        <v>6938078</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,7 +2611,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2620,12 +2621,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,19 +2636,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124981684</v>
+        <v>124988491</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2687,7 +2683,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2696,10 +2697,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587057</v>
+        <v>587193</v>
       </c>
       <c r="R19" t="n">
-        <v>6938054</v>
+        <v>6938003</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2731,7 +2732,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2741,7 +2742,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,22 +2757,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124989520</v>
+        <v>124989553</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2780,38 +2781,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587123</v>
+        <v>587128</v>
       </c>
       <c r="R20" t="n">
-        <v>6937980</v>
+        <v>6937990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,7 +2853,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2853,7 +2863,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,19 +2878,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124987740</v>
+        <v>124986659</v>
       </c>
       <c r="B21" t="n">
         <v>79891</v>
@@ -2920,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587191</v>
+        <v>587032</v>
       </c>
       <c r="R21" t="n">
-        <v>6938140</v>
+        <v>6938236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2955,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2965,7 +2975,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2992,10 +3002,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124983563</v>
+        <v>124987383</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3008,39 +3018,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586799</v>
+        <v>587108</v>
       </c>
       <c r="R22" t="n">
-        <v>6938055</v>
+        <v>6938215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3072,7 +3077,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3082,12 +3087,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3114,7 +3114,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124988050</v>
+        <v>124982748</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3150,14 +3150,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587221</v>
+        <v>586911</v>
       </c>
       <c r="R23" t="n">
-        <v>6938107</v>
+        <v>6938088</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,10 +3226,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124982589</v>
+        <v>124985931</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3242,34 +3242,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586904</v>
+        <v>587058</v>
       </c>
       <c r="R24" t="n">
-        <v>6938096</v>
+        <v>6938138</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3301,7 +3306,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3311,7 +3316,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,22 +3336,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124982748</v>
+        <v>124985796</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,34 +3364,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586911</v>
+        <v>587080</v>
       </c>
       <c r="R25" t="n">
-        <v>6938088</v>
+        <v>6938107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3423,7 +3433,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3450,7 +3460,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124986178</v>
+        <v>124989520</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3490,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587008</v>
+        <v>587123</v>
       </c>
       <c r="R26" t="n">
-        <v>6938211</v>
+        <v>6937980</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3525,7 +3535,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3535,7 +3545,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,10 +3572,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124987424</v>
+        <v>124988050</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,39 +3588,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587103</v>
+        <v>587221</v>
       </c>
       <c r="R27" t="n">
-        <v>6938206</v>
+        <v>6938107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,7 +3647,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3652,7 +3657,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3667,22 +3672,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124988491</v>
+        <v>124988914</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3691,35 +3696,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3731,7 +3732,7 @@
         <v>587193</v>
       </c>
       <c r="R28" t="n">
-        <v>6938003</v>
+        <v>6937956</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3763,7 +3764,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3773,7 +3774,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3800,10 +3806,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124987817</v>
+        <v>124981403</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3816,34 +3822,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587218</v>
+        <v>587070</v>
       </c>
       <c r="R29" t="n">
-        <v>6938125</v>
+        <v>6938040</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3875,7 +3886,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3885,7 +3896,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,22 +3916,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124986503</v>
+        <v>124987318</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3928,47 +3944,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587003</v>
+        <v>587102</v>
       </c>
       <c r="R30" t="n">
-        <v>6938230</v>
+        <v>6938235</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3997,7 +4003,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4007,7 +4013,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4022,22 +4028,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124988641</v>
+        <v>124981660</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4050,39 +4056,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587123</v>
+        <v>587048</v>
       </c>
       <c r="R31" t="n">
-        <v>6937990</v>
+        <v>6938056</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4114,7 +4115,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4124,12 +4125,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4156,7 +4152,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124988918</v>
+        <v>124986503</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4190,24 +4186,29 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587221</v>
+        <v>587003</v>
       </c>
       <c r="R32" t="n">
-        <v>6937950</v>
+        <v>6938230</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4236,7 +4237,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4246,12 +4247,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4266,19 +4262,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124983114</v>
+        <v>124988415</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4314,14 +4310,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586836</v>
+        <v>587161</v>
       </c>
       <c r="R33" t="n">
-        <v>6938079</v>
+        <v>6938018</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4353,7 +4349,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4363,7 +4359,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4390,7 +4386,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124988270</v>
+        <v>124987817</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4430,10 +4426,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587190</v>
+        <v>587218</v>
       </c>
       <c r="R34" t="n">
-        <v>6938036</v>
+        <v>6938125</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4465,7 +4461,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4475,7 +4471,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4502,10 +4498,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124987066</v>
+        <v>124988918</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4518,34 +4514,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587081</v>
+        <v>587221</v>
       </c>
       <c r="R35" t="n">
-        <v>6938219</v>
+        <v>6937950</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4577,7 +4578,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4587,7 +4588,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4602,22 +4608,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124988529</v>
+        <v>124985568</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4630,34 +4636,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587145</v>
+        <v>587027</v>
       </c>
       <c r="R36" t="n">
-        <v>6938003</v>
+        <v>6938028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4689,7 +4700,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4699,7 +4710,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4714,19 +4730,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124983267</v>
+        <v>124989421</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4762,14 +4778,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586804</v>
+        <v>587147</v>
       </c>
       <c r="R37" t="n">
-        <v>6938078</v>
+        <v>6937978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4801,7 +4817,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4811,7 +4827,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4826,22 +4842,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124990166</v>
+        <v>124987424</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4850,35 +4866,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4887,10 +4899,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587097</v>
+        <v>587103</v>
       </c>
       <c r="R38" t="n">
-        <v>6937989</v>
+        <v>6938206</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4922,7 +4934,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4932,7 +4944,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4959,10 +4971,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124987383</v>
+        <v>124988969</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4975,34 +4987,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587108</v>
+        <v>587225</v>
       </c>
       <c r="R39" t="n">
-        <v>6938215</v>
+        <v>6937951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5034,7 +5051,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5044,7 +5061,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5071,10 +5093,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124987521</v>
+        <v>124988323</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5087,34 +5109,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587127</v>
+        <v>587174</v>
       </c>
       <c r="R40" t="n">
-        <v>6938166</v>
+        <v>6938028</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5146,7 +5173,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5156,7 +5183,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5183,7 +5215,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124985796</v>
+        <v>124987521</v>
       </c>
       <c r="B41" t="n">
         <v>79891</v>
@@ -5223,10 +5255,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587080</v>
+        <v>587127</v>
       </c>
       <c r="R41" t="n">
-        <v>6938107</v>
+        <v>6938166</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5258,7 +5290,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5268,7 +5300,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5295,7 +5327,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124989421</v>
+        <v>124988529</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5335,10 +5367,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587147</v>
+        <v>587145</v>
       </c>
       <c r="R42" t="n">
-        <v>6937978</v>
+        <v>6938003</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5370,7 +5402,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5380,7 +5412,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5407,10 +5439,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124981283</v>
+        <v>124987125</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5423,39 +5455,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587053</v>
+        <v>587084</v>
       </c>
       <c r="R43" t="n">
-        <v>6938038</v>
+        <v>6938203</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5487,7 +5514,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,12 +5524,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,10 +5551,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124981756</v>
+        <v>124981815</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,31 +5563,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5574,13 +5595,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587045</v>
+        <v>587032</v>
       </c>
       <c r="R44" t="n">
-        <v>6938068</v>
+        <v>6938083</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5609,7 +5630,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5619,12 +5640,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5639,22 +5655,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124988323</v>
+        <v>124981684</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5663,31 +5679,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5696,10 +5711,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587174</v>
+        <v>587057</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938054</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5731,7 +5746,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5741,12 +5756,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5773,10 +5783,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124982003</v>
+        <v>124982787</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5789,34 +5799,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587036</v>
+        <v>586882</v>
       </c>
       <c r="R46" t="n">
-        <v>6938128</v>
+        <v>6938074</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5848,7 +5863,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5858,7 +5873,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5873,22 +5893,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124987125</v>
+        <v>124981283</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5901,34 +5921,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587084</v>
+        <v>587053</v>
       </c>
       <c r="R47" t="n">
-        <v>6938203</v>
+        <v>6938038</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5960,7 +5985,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5970,7 +5995,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5997,10 +6027,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124985568</v>
+        <v>124982003</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6013,39 +6043,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587027</v>
+        <v>587036</v>
       </c>
       <c r="R48" t="n">
-        <v>6938028</v>
+        <v>6938128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6077,7 +6102,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6087,12 +6112,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6107,19 +6127,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124988185</v>
+        <v>124984652</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -6155,14 +6175,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587197</v>
+        <v>586891</v>
       </c>
       <c r="R49" t="n">
-        <v>6938055</v>
+        <v>6937995</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6194,7 +6214,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6224,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6231,10 +6251,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124983653</v>
+        <v>124988270</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6247,39 +6267,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586814</v>
+        <v>587190</v>
       </c>
       <c r="R50" t="n">
-        <v>6938043</v>
+        <v>6938036</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6311,7 +6326,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6321,12 +6336,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6341,22 +6351,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124982289</v>
+        <v>124987066</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6369,39 +6379,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586956</v>
+        <v>587081</v>
       </c>
       <c r="R51" t="n">
-        <v>6938114</v>
+        <v>6938219</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,7 +6438,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6443,12 +6448,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6475,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124982567</v>
+        <v>124986178</v>
       </c>
       <c r="B52" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,34 +6491,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586907</v>
+        <v>587008</v>
       </c>
       <c r="R52" t="n">
-        <v>6938087</v>
+        <v>6938211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987740</v>
+        <v>124987383</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587191</v>
+        <v>587108</v>
       </c>
       <c r="R2" t="n">
-        <v>6938140</v>
+        <v>6938215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124982567</v>
+        <v>124987066</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586907</v>
+        <v>587081</v>
       </c>
       <c r="R3" t="n">
-        <v>6938087</v>
+        <v>6938219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124982589</v>
+        <v>124981850</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586904</v>
+        <v>587051</v>
       </c>
       <c r="R4" t="n">
-        <v>6938096</v>
+        <v>6938101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124983653</v>
+        <v>124988050</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586814</v>
+        <v>587221</v>
       </c>
       <c r="R5" t="n">
-        <v>6938043</v>
+        <v>6938107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983114</v>
+        <v>124989553</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,38 +1135,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586836</v>
+        <v>587128</v>
       </c>
       <c r="R6" t="n">
-        <v>6938079</v>
+        <v>6937990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124982170</v>
+        <v>124987424</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,16 +1260,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1281,19 +1280,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586964</v>
+        <v>587103</v>
       </c>
       <c r="R7" t="n">
-        <v>6938109</v>
+        <v>6938206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987889</v>
+        <v>124982748</v>
       </c>
       <c r="B8" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1373,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587214</v>
+        <v>586911</v>
       </c>
       <c r="R8" t="n">
-        <v>6938134</v>
+        <v>6938088</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124990166</v>
+        <v>124988914</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,35 +1485,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1528,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587097</v>
+        <v>587193</v>
       </c>
       <c r="R9" t="n">
-        <v>6937989</v>
+        <v>6937956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1563,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124981850</v>
+        <v>124987740</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,25 +1607,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1640,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587051</v>
+        <v>587191</v>
       </c>
       <c r="R10" t="n">
-        <v>6938101</v>
+        <v>6938140</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124986918</v>
+        <v>124982567</v>
       </c>
       <c r="B11" t="n">
         <v>91299</v>
@@ -1748,14 +1743,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587054</v>
+        <v>586907</v>
       </c>
       <c r="R11" t="n">
-        <v>6938245</v>
+        <v>6938087</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124982289</v>
+        <v>124988491</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,43 +1831,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586956</v>
+        <v>587193</v>
       </c>
       <c r="R12" t="n">
-        <v>6938114</v>
+        <v>6938003</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,7 +1940,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124988641</v>
+        <v>124981756</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1982,7 +1976,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1991,13 +1985,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587123</v>
+        <v>587045</v>
       </c>
       <c r="R13" t="n">
-        <v>6937990</v>
+        <v>6938068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,12 +2030,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,22 +2050,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124983563</v>
+        <v>124987817</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,39 +2078,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586799</v>
+        <v>587218</v>
       </c>
       <c r="R14" t="n">
-        <v>6938055</v>
+        <v>6938125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,12 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,7 +2174,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124981756</v>
+        <v>124982289</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2226,22 +2210,22 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587045</v>
+        <v>586956</v>
       </c>
       <c r="R15" t="n">
-        <v>6938068</v>
+        <v>6938114</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2270,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,12 +2264,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,10 +2296,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124986538</v>
+        <v>124988529</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,34 +2312,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587003</v>
+        <v>587145</v>
       </c>
       <c r="R16" t="n">
-        <v>6938235</v>
+        <v>6938003</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,22 +2396,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988185</v>
+        <v>124982003</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,21 +2424,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2464,10 +2448,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587197</v>
+        <v>587036</v>
       </c>
       <c r="R17" t="n">
-        <v>6938055</v>
+        <v>6938128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124983267</v>
+        <v>124990166</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2548,38 +2532,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586804</v>
+        <v>587097</v>
       </c>
       <c r="R18" t="n">
-        <v>6938078</v>
+        <v>6937989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2611,7 +2604,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2621,7 +2614,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124988491</v>
+        <v>124986918</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,47 +2653,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587193</v>
+        <v>587054</v>
       </c>
       <c r="R19" t="n">
-        <v>6938003</v>
+        <v>6938245</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2732,7 +2716,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2742,7 +2726,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,22 +2741,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124989553</v>
+        <v>124983267</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2781,47 +2765,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587128</v>
+        <v>586804</v>
       </c>
       <c r="R20" t="n">
-        <v>6937990</v>
+        <v>6938078</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2853,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2863,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124986659</v>
+        <v>124985568</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2906,34 +2881,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587032</v>
+        <v>587027</v>
       </c>
       <c r="R21" t="n">
-        <v>6938236</v>
+        <v>6938028</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2965,7 +2945,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2975,7 +2955,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,22 +2975,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124987383</v>
+        <v>124982787</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3018,34 +3003,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587108</v>
+        <v>586882</v>
       </c>
       <c r="R22" t="n">
-        <v>6938215</v>
+        <v>6938074</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,7 +3067,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3087,7 +3077,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3102,19 +3097,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124982748</v>
+        <v>124983114</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3154,10 +3149,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586911</v>
+        <v>586836</v>
       </c>
       <c r="R23" t="n">
-        <v>6938088</v>
+        <v>6938079</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124985931</v>
+        <v>124986178</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3242,39 +3237,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587058</v>
+        <v>587008</v>
       </c>
       <c r="R24" t="n">
-        <v>6938138</v>
+        <v>6938211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3306,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3316,12 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,7 +3333,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124985796</v>
+        <v>124987318</v>
       </c>
       <c r="B25" t="n">
         <v>79891</v>
@@ -3388,10 +3373,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587080</v>
+        <v>587102</v>
       </c>
       <c r="R25" t="n">
-        <v>6938107</v>
+        <v>6938235</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3423,7 +3408,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,7 +3418,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3460,7 +3445,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124989520</v>
+        <v>124988185</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3500,10 +3485,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587123</v>
+        <v>587197</v>
       </c>
       <c r="R26" t="n">
-        <v>6937980</v>
+        <v>6938055</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3535,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3545,7 +3530,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,7 +3557,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124988050</v>
+        <v>124989421</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3612,10 +3597,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587221</v>
+        <v>587147</v>
       </c>
       <c r="R27" t="n">
-        <v>6938107</v>
+        <v>6937978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3647,7 +3632,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3657,7 +3642,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3684,10 +3669,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124988914</v>
+        <v>124982589</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3700,39 +3685,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587193</v>
+        <v>586904</v>
       </c>
       <c r="R28" t="n">
-        <v>6937956</v>
+        <v>6938096</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3764,7 +3744,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,12 +3754,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3806,10 +3781,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124981403</v>
+        <v>124986659</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3822,39 +3797,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587070</v>
+        <v>587032</v>
       </c>
       <c r="R29" t="n">
-        <v>6938040</v>
+        <v>6938236</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3886,7 +3856,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3896,12 +3866,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3916,22 +3881,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124987318</v>
+        <v>124981660</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3944,21 +3909,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3968,10 +3933,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587102</v>
+        <v>587048</v>
       </c>
       <c r="R30" t="n">
-        <v>6938235</v>
+        <v>6938056</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4003,7 +3968,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4013,7 +3978,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4040,10 +4005,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124981660</v>
+        <v>124987521</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4056,21 +4021,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4080,10 +4045,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587048</v>
+        <v>587127</v>
       </c>
       <c r="R31" t="n">
-        <v>6938056</v>
+        <v>6938166</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4115,7 +4080,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4125,7 +4090,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4152,10 +4117,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124986503</v>
+        <v>124988415</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4168,47 +4133,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587003</v>
+        <v>587161</v>
       </c>
       <c r="R32" t="n">
-        <v>6938230</v>
+        <v>6938018</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4237,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4247,7 +4202,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4262,22 +4217,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124988415</v>
+        <v>124981283</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4290,34 +4245,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587161</v>
+        <v>587053</v>
       </c>
       <c r="R33" t="n">
-        <v>6938018</v>
+        <v>6938038</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4349,7 +4309,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4359,7 +4319,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4386,10 +4351,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124987817</v>
+        <v>124981815</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4398,38 +4363,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587218</v>
+        <v>587032</v>
       </c>
       <c r="R34" t="n">
-        <v>6938125</v>
+        <v>6938083</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4461,7 +4430,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4471,7 +4440,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4498,10 +4467,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124988918</v>
+        <v>124989520</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4514,39 +4483,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587221</v>
+        <v>587123</v>
       </c>
       <c r="R35" t="n">
-        <v>6937950</v>
+        <v>6937980</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4578,7 +4542,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4588,12 +4552,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4620,10 +4579,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124985568</v>
+        <v>124988270</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4636,39 +4595,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587027</v>
+        <v>587190</v>
       </c>
       <c r="R36" t="n">
-        <v>6938028</v>
+        <v>6938036</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4700,7 +4654,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4710,12 +4664,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4730,22 +4679,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124989421</v>
+        <v>124983653</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4758,34 +4707,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587147</v>
+        <v>586814</v>
       </c>
       <c r="R37" t="n">
-        <v>6937978</v>
+        <v>6938043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4817,7 +4771,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4827,7 +4781,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4842,22 +4801,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124987424</v>
+        <v>124987889</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>91457</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4866,43 +4825,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587103</v>
+        <v>587214</v>
       </c>
       <c r="R38" t="n">
-        <v>6938206</v>
+        <v>6938134</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4934,7 +4888,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4944,7 +4898,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,10 +4925,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124988969</v>
+        <v>124984652</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4987,39 +4941,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587225</v>
+        <v>586891</v>
       </c>
       <c r="R39" t="n">
-        <v>6937951</v>
+        <v>6937995</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5051,7 +5000,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5061,12 +5010,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5093,7 +5037,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124988323</v>
+        <v>124986503</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5127,24 +5071,29 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587174</v>
+        <v>587003</v>
       </c>
       <c r="R40" t="n">
-        <v>6938028</v>
+        <v>6938230</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5173,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5183,12 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5203,22 +5147,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124987521</v>
+        <v>124981403</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5231,34 +5175,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587127</v>
+        <v>587070</v>
       </c>
       <c r="R41" t="n">
-        <v>6938166</v>
+        <v>6938040</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5290,7 +5239,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5300,7 +5249,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,22 +5269,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124988529</v>
+        <v>124988918</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5343,34 +5297,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587145</v>
+        <v>587221</v>
       </c>
       <c r="R42" t="n">
-        <v>6938003</v>
+        <v>6937950</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5402,7 +5361,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5412,7 +5371,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5439,10 +5403,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124987125</v>
+        <v>124982170</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5455,34 +5419,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587084</v>
+        <v>586964</v>
       </c>
       <c r="R43" t="n">
-        <v>6938203</v>
+        <v>6938109</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5514,7 +5483,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5524,7 +5493,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5539,22 +5513,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124981815</v>
+        <v>124988969</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5563,30 +5537,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5595,10 +5570,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587032</v>
+        <v>587225</v>
       </c>
       <c r="R44" t="n">
-        <v>6938083</v>
+        <v>6937951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5630,7 +5605,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5640,7 +5615,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,10 +5647,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124981684</v>
+        <v>124988323</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5679,30 +5659,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5711,10 +5692,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587057</v>
+        <v>587174</v>
       </c>
       <c r="R45" t="n">
-        <v>6938054</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5746,7 +5727,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5756,7 +5737,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5783,7 +5769,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124982787</v>
+        <v>124988641</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5819,19 +5805,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586882</v>
+        <v>587123</v>
       </c>
       <c r="R46" t="n">
-        <v>6938074</v>
+        <v>6937990</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5863,7 +5849,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5873,7 +5859,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5893,22 +5879,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124981283</v>
+        <v>124986538</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5921,39 +5907,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587053</v>
+        <v>587003</v>
       </c>
       <c r="R47" t="n">
-        <v>6938038</v>
+        <v>6938235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5985,7 +5966,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5995,12 +5976,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6015,19 +5991,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124982003</v>
+        <v>124987125</v>
       </c>
       <c r="B48" t="n">
         <v>79891</v>
@@ -6067,10 +6043,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587036</v>
+        <v>587084</v>
       </c>
       <c r="R48" t="n">
-        <v>6938128</v>
+        <v>6938203</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6102,7 +6078,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6112,7 +6088,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6139,10 +6115,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124984652</v>
+        <v>124981684</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6151,38 +6127,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586891</v>
+        <v>587057</v>
       </c>
       <c r="R49" t="n">
-        <v>6937995</v>
+        <v>6938054</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6214,7 +6194,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6224,7 +6204,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6251,10 +6231,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124988270</v>
+        <v>124985796</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6267,21 +6247,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6291,10 +6271,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587190</v>
+        <v>587080</v>
       </c>
       <c r="R50" t="n">
-        <v>6938036</v>
+        <v>6938107</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6326,7 +6306,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6336,7 +6316,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6363,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124987066</v>
+        <v>124983563</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6379,34 +6359,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587081</v>
+        <v>586799</v>
       </c>
       <c r="R51" t="n">
-        <v>6938219</v>
+        <v>6938055</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6438,7 +6423,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6448,7 +6433,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6463,22 +6453,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124986178</v>
+        <v>124985931</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,34 +6481,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587008</v>
+        <v>587058</v>
       </c>
       <c r="R52" t="n">
-        <v>6938211</v>
+        <v>6938138</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6545,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6555,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988050</v>
+        <v>124989553</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587221</v>
+        <v>587128</v>
       </c>
       <c r="R5" t="n">
-        <v>6938107</v>
+        <v>6937990</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124989553</v>
+        <v>124988050</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,47 +1144,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587128</v>
+        <v>587221</v>
       </c>
       <c r="R6" t="n">
-        <v>6937990</v>
+        <v>6938107</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124982748</v>
+        <v>124988914</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1377,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586911</v>
+        <v>587193</v>
       </c>
       <c r="R8" t="n">
-        <v>6938088</v>
+        <v>6937956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1471,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124988914</v>
+        <v>124982748</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587193</v>
+        <v>586911</v>
       </c>
       <c r="R9" t="n">
-        <v>6937956</v>
+        <v>6938088</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,12 +1583,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124990166</v>
+        <v>124986918</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,47 +2532,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587097</v>
+        <v>587054</v>
       </c>
       <c r="R18" t="n">
-        <v>6937989</v>
+        <v>6938245</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2614,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,22 +2620,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124986918</v>
+        <v>124990166</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,38 +2644,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587054</v>
+        <v>587097</v>
       </c>
       <c r="R19" t="n">
-        <v>6938245</v>
+        <v>6937989</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,22 +2741,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124983267</v>
+        <v>124985568</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,34 +2769,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586804</v>
+        <v>587027</v>
       </c>
       <c r="R20" t="n">
-        <v>6938078</v>
+        <v>6938028</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2828,7 +2833,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2843,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124985568</v>
+        <v>124983267</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,39 +2891,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587027</v>
+        <v>586804</v>
       </c>
       <c r="R21" t="n">
-        <v>6938028</v>
+        <v>6938078</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2950,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,12 +2960,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124982787</v>
+        <v>124983114</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,39 +3003,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586882</v>
+        <v>586836</v>
       </c>
       <c r="R22" t="n">
-        <v>6938074</v>
+        <v>6938079</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3067,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3077,12 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,22 +3087,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124983114</v>
+        <v>124982787</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3125,34 +3115,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586836</v>
+        <v>586882</v>
       </c>
       <c r="R23" t="n">
-        <v>6938079</v>
+        <v>6938074</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3179,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3189,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,12 +3209,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124985796</v>
+        <v>124983563</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6247,34 +6247,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587080</v>
+        <v>586799</v>
       </c>
       <c r="R50" t="n">
-        <v>6938107</v>
+        <v>6938055</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6306,7 +6311,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6316,7 +6321,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6343,7 +6353,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124983563</v>
+        <v>124985931</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6379,19 +6389,19 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586799</v>
+        <v>587058</v>
       </c>
       <c r="R51" t="n">
-        <v>6938055</v>
+        <v>6938138</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6423,7 +6433,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6433,7 +6443,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6465,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124985931</v>
+        <v>124985796</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6481,39 +6491,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587058</v>
+        <v>587080</v>
       </c>
       <c r="R52" t="n">
-        <v>6938138</v>
+        <v>6938107</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6545,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6555,12 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987383</v>
+        <v>124981850</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98122</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587108</v>
+        <v>587051</v>
       </c>
       <c r="R2" t="n">
-        <v>6938215</v>
+        <v>6938101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987066</v>
+        <v>124987383</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587081</v>
+        <v>587108</v>
       </c>
       <c r="R3" t="n">
-        <v>6938219</v>
+        <v>6938215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981850</v>
+        <v>124987066</v>
       </c>
       <c r="B4" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587051</v>
+        <v>587081</v>
       </c>
       <c r="R4" t="n">
-        <v>6938101</v>
+        <v>6938219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124989553</v>
+        <v>124988050</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587128</v>
+        <v>587221</v>
       </c>
       <c r="R5" t="n">
-        <v>6937990</v>
+        <v>6938107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124988050</v>
+        <v>124989553</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,38 +1135,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587221</v>
+        <v>587128</v>
       </c>
       <c r="R6" t="n">
-        <v>6938107</v>
+        <v>6937990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124987740</v>
+        <v>124988491</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,38 +1607,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587191</v>
+        <v>587193</v>
       </c>
       <c r="R10" t="n">
-        <v>6938140</v>
+        <v>6938003</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,12 +1704,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1819,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124988491</v>
+        <v>124987740</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,47 +1840,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587193</v>
+        <v>587191</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938140</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,12 +1928,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124988529</v>
+        <v>124986918</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587145</v>
+        <v>587054</v>
       </c>
       <c r="R16" t="n">
-        <v>6938003</v>
+        <v>6938245</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124982003</v>
+        <v>124988529</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,21 +2424,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587036</v>
+        <v>587145</v>
       </c>
       <c r="R17" t="n">
-        <v>6938128</v>
+        <v>6938003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124986918</v>
+        <v>124982003</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587054</v>
+        <v>587036</v>
       </c>
       <c r="R18" t="n">
-        <v>6938245</v>
+        <v>6938128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2987,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124983114</v>
+        <v>124982787</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,34 +3003,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586836</v>
+        <v>586882</v>
       </c>
       <c r="R22" t="n">
-        <v>6938079</v>
+        <v>6938074</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,7 +3067,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3077,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,22 +3097,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124982787</v>
+        <v>124983114</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3115,39 +3125,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586882</v>
+        <v>586836</v>
       </c>
       <c r="R23" t="n">
-        <v>6938074</v>
+        <v>6938079</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3179,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3189,12 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,12 +3209,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981850</v>
+        <v>124988491</v>
       </c>
       <c r="B2" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587051</v>
+        <v>587193</v>
       </c>
       <c r="R2" t="n">
-        <v>6938101</v>
+        <v>6938003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987383</v>
+        <v>124985796</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587108</v>
+        <v>587080</v>
       </c>
       <c r="R3" t="n">
-        <v>6938215</v>
+        <v>6938107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987066</v>
+        <v>124986503</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +924,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587081</v>
+        <v>587003</v>
       </c>
       <c r="R4" t="n">
-        <v>6938219</v>
+        <v>6938230</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988050</v>
+        <v>124981756</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1046,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587221</v>
+        <v>587045</v>
       </c>
       <c r="R5" t="n">
-        <v>6938107</v>
+        <v>6938068</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1140,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124989553</v>
+        <v>124982289</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,47 +1164,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587128</v>
+        <v>586956</v>
       </c>
       <c r="R6" t="n">
-        <v>6937990</v>
+        <v>6938114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124987424</v>
+        <v>124988641</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,16 +1290,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1289,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587103</v>
+        <v>587123</v>
       </c>
       <c r="R7" t="n">
-        <v>6938206</v>
+        <v>6937990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1384,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124988914</v>
+        <v>124988050</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1412,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587193</v>
+        <v>587221</v>
       </c>
       <c r="R8" t="n">
-        <v>6937956</v>
+        <v>6938107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,22 +1496,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124982748</v>
+        <v>124989553</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,38 +1520,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586911</v>
+        <v>587128</v>
       </c>
       <c r="R9" t="n">
-        <v>6938088</v>
+        <v>6937990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124988491</v>
+        <v>124981850</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,47 +1641,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587193</v>
+        <v>587051</v>
       </c>
       <c r="R10" t="n">
-        <v>6938003</v>
+        <v>6938101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1729,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124982567</v>
+        <v>124988270</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,34 +1757,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586907</v>
+        <v>587190</v>
       </c>
       <c r="R11" t="n">
-        <v>6938087</v>
+        <v>6938036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987740</v>
+        <v>124990166</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,38 +1865,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587191</v>
+        <v>587097</v>
       </c>
       <c r="R12" t="n">
-        <v>6938140</v>
+        <v>6937989</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1947,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,22 +1962,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124981756</v>
+        <v>124981684</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,31 +1986,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1985,13 +2018,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587045</v>
+        <v>587057</v>
       </c>
       <c r="R13" t="n">
-        <v>6938068</v>
+        <v>6938054</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,12 +2063,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,19 +2078,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987817</v>
+        <v>124988415</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2102,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587218</v>
+        <v>587161</v>
       </c>
       <c r="R14" t="n">
-        <v>6938125</v>
+        <v>6938018</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2165,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2175,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124982289</v>
+        <v>124989520</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,39 +2218,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586956</v>
+        <v>587123</v>
       </c>
       <c r="R15" t="n">
-        <v>6938114</v>
+        <v>6937980</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,12 +2287,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,22 +2302,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124986918</v>
+        <v>124983267</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,34 +2330,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587054</v>
+        <v>586804</v>
       </c>
       <c r="R16" t="n">
-        <v>6938245</v>
+        <v>6938078</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2389,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2399,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,22 +2414,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988529</v>
+        <v>124985568</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,34 +2442,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587145</v>
+        <v>587027</v>
       </c>
       <c r="R17" t="n">
-        <v>6938003</v>
+        <v>6938028</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2506,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2516,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,12 +2536,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2632,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124990166</v>
+        <v>124983114</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,47 +2672,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587097</v>
+        <v>586836</v>
       </c>
       <c r="R19" t="n">
-        <v>6937989</v>
+        <v>6938079</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2726,7 +2745,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,22 +2760,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124985568</v>
+        <v>124988529</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,39 +2788,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587027</v>
+        <v>587145</v>
       </c>
       <c r="R20" t="n">
-        <v>6938028</v>
+        <v>6938003</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2843,12 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,22 +2872,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124983267</v>
+        <v>124982787</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2891,34 +2900,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586804</v>
+        <v>586882</v>
       </c>
       <c r="R21" t="n">
-        <v>6938078</v>
+        <v>6938074</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2950,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2974,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,7 +3006,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124982787</v>
+        <v>124981403</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3023,19 +3042,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586882</v>
+        <v>587070</v>
       </c>
       <c r="R22" t="n">
-        <v>6938074</v>
+        <v>6938040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3067,7 +3086,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3077,7 +3096,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3109,10 +3128,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124983114</v>
+        <v>124981815</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,38 +3140,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586836</v>
+        <v>587032</v>
       </c>
       <c r="R23" t="n">
-        <v>6938079</v>
+        <v>6938083</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3207,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3217,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124986178</v>
+        <v>124987521</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,21 +3260,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3261,10 +3284,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587008</v>
+        <v>587127</v>
       </c>
       <c r="R24" t="n">
-        <v>6938211</v>
+        <v>6938166</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,7 +3356,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124987318</v>
+        <v>124987740</v>
       </c>
       <c r="B25" t="n">
         <v>79891</v>
@@ -3373,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587102</v>
+        <v>587191</v>
       </c>
       <c r="R25" t="n">
-        <v>6938235</v>
+        <v>6938140</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3408,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3418,7 +3441,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3445,10 +3468,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124988185</v>
+        <v>124988914</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3461,34 +3484,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587197</v>
+        <v>587193</v>
       </c>
       <c r="R26" t="n">
-        <v>6938055</v>
+        <v>6937956</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3520,7 +3548,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,7 +3558,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3545,22 +3578,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124989421</v>
+        <v>124988323</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3573,34 +3606,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587147</v>
+        <v>587174</v>
       </c>
       <c r="R27" t="n">
-        <v>6937978</v>
+        <v>6938028</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3632,7 +3670,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3642,7 +3680,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,10 +3712,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124982589</v>
+        <v>124987817</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3685,34 +3728,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586904</v>
+        <v>587218</v>
       </c>
       <c r="R28" t="n">
-        <v>6938096</v>
+        <v>6938125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,7 +3787,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3754,7 +3797,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3769,22 +3812,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124986659</v>
+        <v>124986918</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3797,21 +3840,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3821,10 +3864,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587032</v>
+        <v>587054</v>
       </c>
       <c r="R29" t="n">
-        <v>6938236</v>
+        <v>6938245</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,7 +3899,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3866,7 +3909,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3893,10 +3936,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124981660</v>
+        <v>124986538</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3909,34 +3952,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587048</v>
+        <v>587003</v>
       </c>
       <c r="R30" t="n">
-        <v>6938056</v>
+        <v>6938235</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3968,7 +4011,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3978,7 +4021,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3993,22 +4036,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124987521</v>
+        <v>124981283</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4021,34 +4064,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587127</v>
+        <v>587053</v>
       </c>
       <c r="R31" t="n">
-        <v>6938166</v>
+        <v>6938038</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4080,7 +4128,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4090,7 +4138,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4117,10 +4170,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124988415</v>
+        <v>124982589</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4133,34 +4186,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587161</v>
+        <v>586904</v>
       </c>
       <c r="R32" t="n">
-        <v>6938018</v>
+        <v>6938096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4192,7 +4245,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,7 +4255,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4217,22 +4270,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124981283</v>
+        <v>124987125</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4245,39 +4298,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587053</v>
+        <v>587084</v>
       </c>
       <c r="R33" t="n">
-        <v>6938038</v>
+        <v>6938203</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4309,7 +4357,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4319,12 +4367,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4351,10 +4394,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124981815</v>
+        <v>124981660</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4363,42 +4406,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587032</v>
+        <v>587048</v>
       </c>
       <c r="R34" t="n">
-        <v>6938083</v>
+        <v>6938056</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4430,7 +4469,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4440,7 +4479,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4467,10 +4506,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124989520</v>
+        <v>124982170</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,34 +4522,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587123</v>
+        <v>586964</v>
       </c>
       <c r="R35" t="n">
-        <v>6937980</v>
+        <v>6938109</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4542,7 +4586,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4552,7 +4596,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4567,19 +4616,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124988270</v>
+        <v>124984652</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4615,14 +4664,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587190</v>
+        <v>586891</v>
       </c>
       <c r="R36" t="n">
-        <v>6938036</v>
+        <v>6937995</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4654,7 +4703,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4664,7 +4713,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4691,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124983653</v>
+        <v>124987424</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4707,16 +4756,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4732,14 +4781,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586814</v>
+        <v>587103</v>
       </c>
       <c r="R37" t="n">
-        <v>6938043</v>
+        <v>6938206</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4771,7 +4820,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4781,12 +4830,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4813,10 +4857,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124987889</v>
+        <v>124987383</v>
       </c>
       <c r="B38" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4825,25 +4869,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4853,10 +4897,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587214</v>
+        <v>587108</v>
       </c>
       <c r="R38" t="n">
-        <v>6938134</v>
+        <v>6938215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4888,7 +4932,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4898,7 +4942,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4913,22 +4957,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124984652</v>
+        <v>124983653</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4941,34 +4985,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586891</v>
+        <v>586814</v>
       </c>
       <c r="R39" t="n">
-        <v>6937995</v>
+        <v>6938043</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5000,7 +5049,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5010,7 +5059,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5025,22 +5079,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124986503</v>
+        <v>124987889</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5049,51 +5103,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587003</v>
+        <v>587214</v>
       </c>
       <c r="R40" t="n">
-        <v>6938230</v>
+        <v>6938134</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5122,7 +5166,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5176,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5159,10 +5203,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124981403</v>
+        <v>124987318</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5175,39 +5219,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587070</v>
+        <v>587102</v>
       </c>
       <c r="R41" t="n">
-        <v>6938040</v>
+        <v>6938235</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5239,7 +5278,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5249,12 +5288,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5269,22 +5303,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124988918</v>
+        <v>124982748</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5297,39 +5331,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587221</v>
+        <v>586911</v>
       </c>
       <c r="R42" t="n">
-        <v>6937950</v>
+        <v>6938088</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5361,7 +5390,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5371,12 +5400,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5403,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124982170</v>
+        <v>124986659</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5419,39 +5443,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586964</v>
+        <v>587032</v>
       </c>
       <c r="R43" t="n">
-        <v>6938109</v>
+        <v>6938236</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5483,7 +5502,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5493,12 +5512,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5513,22 +5527,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124988969</v>
+        <v>124988185</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,39 +5555,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587225</v>
+        <v>587197</v>
       </c>
       <c r="R44" t="n">
-        <v>6937951</v>
+        <v>6938055</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5605,7 +5614,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5615,12 +5624,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5647,10 +5651,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124988323</v>
+        <v>124989421</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5663,39 +5667,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587174</v>
+        <v>587147</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6937978</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5727,7 +5726,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5737,12 +5736,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5769,7 +5763,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124988641</v>
+        <v>124985931</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5805,7 +5799,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5814,10 +5808,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587123</v>
+        <v>587058</v>
       </c>
       <c r="R46" t="n">
-        <v>6937990</v>
+        <v>6938138</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5849,7 +5843,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5859,7 +5853,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5891,7 +5885,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124986538</v>
+        <v>124987066</v>
       </c>
       <c r="B47" t="n">
         <v>79891</v>
@@ -5927,14 +5921,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587003</v>
+        <v>587081</v>
       </c>
       <c r="R47" t="n">
-        <v>6938235</v>
+        <v>6938219</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5966,7 +5960,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5976,7 +5970,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6003,10 +5997,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124987125</v>
+        <v>124986178</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6019,21 +6013,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6043,10 +6037,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587084</v>
+        <v>587008</v>
       </c>
       <c r="R48" t="n">
-        <v>6938203</v>
+        <v>6938211</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6078,7 +6072,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6088,7 +6082,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6115,10 +6109,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124981684</v>
+        <v>124983563</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6127,42 +6121,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587057</v>
+        <v>586799</v>
       </c>
       <c r="R49" t="n">
-        <v>6938054</v>
+        <v>6938055</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6194,7 +6189,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6199,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6231,7 +6231,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124983563</v>
+        <v>124988918</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6272,14 +6272,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586799</v>
+        <v>587221</v>
       </c>
       <c r="R50" t="n">
-        <v>6938055</v>
+        <v>6937950</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6353,7 +6353,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124985931</v>
+        <v>124988969</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587058</v>
+        <v>587225</v>
       </c>
       <c r="R51" t="n">
-        <v>6938138</v>
+        <v>6937951</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6475,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124985796</v>
+        <v>124982567</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,34 +6491,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587080</v>
+        <v>586907</v>
       </c>
       <c r="R52" t="n">
-        <v>6938107</v>
+        <v>6938087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124988491</v>
+        <v>124988641</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587193</v>
+        <v>587123</v>
       </c>
       <c r="R2" t="n">
-        <v>6938003</v>
+        <v>6937990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124985796</v>
+        <v>124981684</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +809,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587080</v>
+        <v>587057</v>
       </c>
       <c r="R3" t="n">
-        <v>6938107</v>
+        <v>6938054</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124986503</v>
+        <v>124985796</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,47 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587003</v>
+        <v>587080</v>
       </c>
       <c r="R4" t="n">
-        <v>6938230</v>
+        <v>6938107</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124981756</v>
+        <v>124986503</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1064,24 +1059,29 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587045</v>
+        <v>587003</v>
       </c>
       <c r="R5" t="n">
-        <v>6938068</v>
+        <v>6938230</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124982289</v>
+        <v>124988914</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1193,14 +1188,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586956</v>
+        <v>587193</v>
       </c>
       <c r="R6" t="n">
-        <v>6938114</v>
+        <v>6937956</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988641</v>
+        <v>124989553</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,31 +1281,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,7 +1318,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587123</v>
+        <v>587128</v>
       </c>
       <c r="R7" t="n">
         <v>6937990</v>
@@ -1354,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,22 +1378,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124988050</v>
+        <v>124987066</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,21 +1406,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1436,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587221</v>
+        <v>587081</v>
       </c>
       <c r="R8" t="n">
-        <v>6938107</v>
+        <v>6938219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,22 +1490,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124989553</v>
+        <v>124988323</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,35 +1514,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1557,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587128</v>
+        <v>587174</v>
       </c>
       <c r="R9" t="n">
-        <v>6937990</v>
+        <v>6938028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1592,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1612,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124981850</v>
+        <v>124990166</v>
       </c>
       <c r="B10" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,38 +1636,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587051</v>
+        <v>587097</v>
       </c>
       <c r="R10" t="n">
-        <v>6938101</v>
+        <v>6937989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,22 +1733,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124988270</v>
+        <v>124987125</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,21 +1761,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1781,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587190</v>
+        <v>587084</v>
       </c>
       <c r="R11" t="n">
-        <v>6938036</v>
+        <v>6938203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124990166</v>
+        <v>124988918</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,35 +1869,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587097</v>
+        <v>587221</v>
       </c>
       <c r="R12" t="n">
-        <v>6937989</v>
+        <v>6937950</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,7 +1947,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,19 +1967,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124981684</v>
+        <v>124981815</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2018,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587057</v>
+        <v>587032</v>
       </c>
       <c r="R13" t="n">
-        <v>6938054</v>
+        <v>6938083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,7 +2095,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988415</v>
+        <v>124988270</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2130,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587161</v>
+        <v>587190</v>
       </c>
       <c r="R14" t="n">
-        <v>6938018</v>
+        <v>6938036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2180,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,7 +2207,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124989520</v>
+        <v>124984652</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2238,14 +2243,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587123</v>
+        <v>586891</v>
       </c>
       <c r="R15" t="n">
-        <v>6937980</v>
+        <v>6937995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,7 +2292,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124983267</v>
+        <v>124981850</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,38 +2331,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586804</v>
+        <v>587051</v>
       </c>
       <c r="R16" t="n">
-        <v>6938078</v>
+        <v>6938101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,7 +2394,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,7 +2404,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,22 +2419,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124985568</v>
+        <v>124986538</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,39 +2447,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587027</v>
+        <v>587003</v>
       </c>
       <c r="R17" t="n">
-        <v>6938028</v>
+        <v>6938235</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,12 +2516,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,10 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124982003</v>
+        <v>124988185</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,21 +2559,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587036</v>
+        <v>587197</v>
       </c>
       <c r="R18" t="n">
-        <v>6938128</v>
+        <v>6938055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,7 +2618,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2633,7 +2628,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,10 +2655,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124983114</v>
+        <v>124981403</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2676,34 +2671,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586836</v>
+        <v>587070</v>
       </c>
       <c r="R19" t="n">
-        <v>6938079</v>
+        <v>6938040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,7 +2745,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2760,22 +2765,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124988529</v>
+        <v>124983563</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2788,34 +2793,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587145</v>
+        <v>586799</v>
       </c>
       <c r="R20" t="n">
-        <v>6938003</v>
+        <v>6938055</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2847,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,7 +2867,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,7 +2899,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124982787</v>
+        <v>124985931</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2925,14 +2940,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586882</v>
+        <v>587058</v>
       </c>
       <c r="R21" t="n">
-        <v>6938074</v>
+        <v>6938138</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2979,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,7 +2989,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2994,22 +3009,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124981403</v>
+        <v>124987740</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3022,39 +3037,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587070</v>
+        <v>587191</v>
       </c>
       <c r="R22" t="n">
-        <v>6938040</v>
+        <v>6938140</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3086,7 +3096,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3096,12 +3106,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,22 +3121,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124981815</v>
+        <v>124987889</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3144,38 +3149,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587032</v>
+        <v>587214</v>
       </c>
       <c r="R23" t="n">
-        <v>6938083</v>
+        <v>6938134</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3207,7 +3208,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3217,7 +3218,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3232,12 +3233,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3356,10 +3357,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124987740</v>
+        <v>124988050</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3372,21 +3373,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3396,10 +3397,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587191</v>
+        <v>587221</v>
       </c>
       <c r="R25" t="n">
-        <v>6938140</v>
+        <v>6938107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3432,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,7 +3442,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3468,10 +3469,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124988914</v>
+        <v>124988415</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3484,39 +3485,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587193</v>
+        <v>587161</v>
       </c>
       <c r="R26" t="n">
-        <v>6937956</v>
+        <v>6938018</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,7 +3544,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3558,12 +3554,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3578,22 +3569,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124988323</v>
+        <v>124982589</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3606,39 +3597,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587174</v>
+        <v>586904</v>
       </c>
       <c r="R27" t="n">
-        <v>6938028</v>
+        <v>6938096</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3670,7 +3656,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3680,12 +3666,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,19 +3681,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124987817</v>
+        <v>124989421</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3752,10 +3733,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587218</v>
+        <v>587147</v>
       </c>
       <c r="R28" t="n">
-        <v>6938125</v>
+        <v>6937978</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3787,7 +3768,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3797,7 +3778,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3824,10 +3805,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124986918</v>
+        <v>124987817</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3840,21 +3821,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3864,10 +3845,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587054</v>
+        <v>587218</v>
       </c>
       <c r="R29" t="n">
-        <v>6938245</v>
+        <v>6938125</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3899,7 +3880,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3909,7 +3890,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3936,10 +3917,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124986538</v>
+        <v>124982787</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,34 +3933,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587003</v>
+        <v>586882</v>
       </c>
       <c r="R30" t="n">
-        <v>6938235</v>
+        <v>6938074</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4011,7 +3997,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4021,7 +4007,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,10 +4039,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124981283</v>
+        <v>124989520</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4064,39 +4055,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587053</v>
+        <v>587123</v>
       </c>
       <c r="R31" t="n">
-        <v>6938038</v>
+        <v>6937980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4128,7 +4114,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4138,12 +4124,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4170,10 +4151,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124982589</v>
+        <v>124982748</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4186,21 +4167,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4210,10 +4191,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586904</v>
+        <v>586911</v>
       </c>
       <c r="R32" t="n">
-        <v>6938096</v>
+        <v>6938088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4245,7 +4226,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4255,7 +4236,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4270,22 +4251,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124987125</v>
+        <v>124983267</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4298,34 +4279,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587084</v>
+        <v>586804</v>
       </c>
       <c r="R33" t="n">
-        <v>6938203</v>
+        <v>6938078</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4357,7 +4338,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4367,7 +4348,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4382,22 +4363,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124981660</v>
+        <v>124988491</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4406,38 +4387,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587048</v>
+        <v>587193</v>
       </c>
       <c r="R34" t="n">
-        <v>6938056</v>
+        <v>6938003</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4469,7 +4459,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4479,7 +4469,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4494,19 +4484,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124982170</v>
+        <v>124983653</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4542,19 +4532,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586964</v>
+        <v>586814</v>
       </c>
       <c r="R35" t="n">
-        <v>6938109</v>
+        <v>6938043</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4586,7 +4576,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4596,7 +4586,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4628,10 +4618,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124984652</v>
+        <v>124988969</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4644,34 +4634,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586891</v>
+        <v>587225</v>
       </c>
       <c r="R36" t="n">
-        <v>6937995</v>
+        <v>6937951</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4703,7 +4698,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4713,7 +4708,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124987424</v>
+        <v>124988529</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4756,39 +4756,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587103</v>
+        <v>587145</v>
       </c>
       <c r="R37" t="n">
-        <v>6938206</v>
+        <v>6938003</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4820,7 +4815,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4830,7 +4825,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4845,22 +4840,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124987383</v>
+        <v>124982170</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4873,34 +4868,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587108</v>
+        <v>586964</v>
       </c>
       <c r="R38" t="n">
-        <v>6938215</v>
+        <v>6938109</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4942,7 +4942,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4957,22 +4962,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124983653</v>
+        <v>124987424</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4985,16 +4990,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5010,14 +5015,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586814</v>
+        <v>587103</v>
       </c>
       <c r="R39" t="n">
-        <v>6938043</v>
+        <v>6938206</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5049,7 +5054,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5059,12 +5064,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124987889</v>
+        <v>124987318</v>
       </c>
       <c r="B40" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,25 +5103,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587214</v>
+        <v>587102</v>
       </c>
       <c r="R40" t="n">
-        <v>6938134</v>
+        <v>6938235</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5191,19 +5191,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124987318</v>
+        <v>124987383</v>
       </c>
       <c r="B41" t="n">
         <v>79891</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587102</v>
+        <v>587108</v>
       </c>
       <c r="R41" t="n">
-        <v>6938235</v>
+        <v>6938215</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,7 +5315,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124982748</v>
+        <v>124981660</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5351,14 +5351,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586911</v>
+        <v>587048</v>
       </c>
       <c r="R42" t="n">
-        <v>6938088</v>
+        <v>6938056</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124986659</v>
+        <v>124982567</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,34 +5443,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587032</v>
+        <v>586907</v>
       </c>
       <c r="R43" t="n">
-        <v>6938236</v>
+        <v>6938087</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5539,7 +5539,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124988185</v>
+        <v>124986178</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587197</v>
+        <v>587008</v>
       </c>
       <c r="R44" t="n">
-        <v>6938055</v>
+        <v>6938211</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5651,10 +5651,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124989421</v>
+        <v>124982289</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5667,34 +5667,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587147</v>
+        <v>586956</v>
       </c>
       <c r="R45" t="n">
-        <v>6937978</v>
+        <v>6938114</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5726,7 +5731,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5736,7 +5741,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5751,19 +5761,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124985931</v>
+        <v>124985568</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5799,19 +5809,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587058</v>
+        <v>587027</v>
       </c>
       <c r="R46" t="n">
-        <v>6938138</v>
+        <v>6938028</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5843,7 +5853,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5853,12 +5863,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5873,22 +5883,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124987066</v>
+        <v>124981756</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5901,37 +5911,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587081</v>
+        <v>587045</v>
       </c>
       <c r="R47" t="n">
-        <v>6938219</v>
+        <v>6938068</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5960,7 +5975,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5970,7 +5985,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5997,10 +6017,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124986178</v>
+        <v>124981283</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6013,34 +6033,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587008</v>
+        <v>587053</v>
       </c>
       <c r="R48" t="n">
-        <v>6938211</v>
+        <v>6938038</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6072,7 +6097,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6082,7 +6107,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6109,10 +6139,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124983563</v>
+        <v>124986918</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6125,39 +6155,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586799</v>
+        <v>587054</v>
       </c>
       <c r="R49" t="n">
-        <v>6938055</v>
+        <v>6938245</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6189,7 +6214,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6199,12 +6224,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6231,10 +6251,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124988918</v>
+        <v>124982003</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6247,39 +6267,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587221</v>
+        <v>587036</v>
       </c>
       <c r="R50" t="n">
-        <v>6937950</v>
+        <v>6938128</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6311,7 +6326,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6321,12 +6336,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6353,10 +6363,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124988969</v>
+        <v>124983114</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6369,39 +6379,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587225</v>
+        <v>586836</v>
       </c>
       <c r="R51" t="n">
-        <v>6937951</v>
+        <v>6938079</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,7 +6438,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6443,12 +6448,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6475,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124982567</v>
+        <v>124986659</v>
       </c>
       <c r="B52" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,34 +6491,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586907</v>
+        <v>587032</v>
       </c>
       <c r="R52" t="n">
-        <v>6938087</v>
+        <v>6938236</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124988641</v>
+        <v>124988491</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587123</v>
+        <v>587193</v>
       </c>
       <c r="R2" t="n">
-        <v>6937990</v>
+        <v>6938003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981684</v>
+        <v>124987817</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,42 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587057</v>
+        <v>587218</v>
       </c>
       <c r="R3" t="n">
-        <v>6938054</v>
+        <v>6938125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124985796</v>
+        <v>124982170</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,34 +924,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587080</v>
+        <v>586964</v>
       </c>
       <c r="R4" t="n">
-        <v>6938107</v>
+        <v>6938109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124986503</v>
+        <v>124987424</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,29 +1064,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587003</v>
+        <v>587103</v>
       </c>
       <c r="R5" t="n">
-        <v>6938230</v>
+        <v>6938206</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124988914</v>
+        <v>124985931</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1183,7 +1183,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587193</v>
+        <v>587058</v>
       </c>
       <c r="R6" t="n">
-        <v>6937956</v>
+        <v>6938138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1257,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124989553</v>
+        <v>124988641</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,35 +1281,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1318,7 +1314,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587128</v>
+        <v>587123</v>
       </c>
       <c r="R7" t="n">
         <v>6937990</v>
@@ -1353,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1359,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987066</v>
+        <v>124986918</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1430,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587081</v>
+        <v>587054</v>
       </c>
       <c r="R8" t="n">
-        <v>6938219</v>
+        <v>6938245</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124988323</v>
+        <v>124983267</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,39 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587174</v>
+        <v>586804</v>
       </c>
       <c r="R9" t="n">
-        <v>6938028</v>
+        <v>6938078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,12 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,22 +1603,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124990166</v>
+        <v>124987383</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,47 +1627,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587097</v>
+        <v>587108</v>
       </c>
       <c r="R10" t="n">
-        <v>6937989</v>
+        <v>6938215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,22 +1715,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987125</v>
+        <v>124988529</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,21 +1743,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587084</v>
+        <v>587145</v>
       </c>
       <c r="R11" t="n">
-        <v>6938203</v>
+        <v>6938003</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,7 +1839,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124988918</v>
+        <v>124983563</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1898,14 +1880,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587221</v>
+        <v>586799</v>
       </c>
       <c r="R12" t="n">
-        <v>6937950</v>
+        <v>6938055</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,7 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1979,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124981815</v>
+        <v>124988415</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1991,42 +1973,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587032</v>
+        <v>587161</v>
       </c>
       <c r="R13" t="n">
-        <v>6938083</v>
+        <v>6938018</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988270</v>
+        <v>124987318</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,21 +2089,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2135,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587190</v>
+        <v>587102</v>
       </c>
       <c r="R14" t="n">
-        <v>6938036</v>
+        <v>6938235</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124984652</v>
+        <v>124982003</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,34 +2201,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586891</v>
+        <v>587036</v>
       </c>
       <c r="R15" t="n">
-        <v>6937995</v>
+        <v>6938128</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2282,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2292,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124981850</v>
+        <v>124990166</v>
       </c>
       <c r="B16" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,38 +2309,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587051</v>
+        <v>587097</v>
       </c>
       <c r="R16" t="n">
-        <v>6938101</v>
+        <v>6937989</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2394,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2404,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,22 +2406,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124986538</v>
+        <v>124989553</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,38 +2430,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587003</v>
+        <v>587128</v>
       </c>
       <c r="R17" t="n">
-        <v>6938235</v>
+        <v>6937990</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,7 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988185</v>
+        <v>124986538</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,34 +2555,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587197</v>
+        <v>587003</v>
       </c>
       <c r="R18" t="n">
-        <v>6938055</v>
+        <v>6938235</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2628,7 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,19 +2639,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124981403</v>
+        <v>124986503</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2689,24 +2685,29 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587070</v>
+        <v>587003</v>
       </c>
       <c r="R19" t="n">
-        <v>6938040</v>
+        <v>6938230</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2735,7 +2736,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2745,12 +2746,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2777,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124983563</v>
+        <v>124982589</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2793,39 +2789,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586799</v>
+        <v>586904</v>
       </c>
       <c r="R20" t="n">
-        <v>6938055</v>
+        <v>6938096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,7 +2848,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,12 +2858,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,22 +2873,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124985931</v>
+        <v>124981850</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2911,43 +2897,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587058</v>
+        <v>587051</v>
       </c>
       <c r="R21" t="n">
-        <v>6938138</v>
+        <v>6938101</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2979,7 +2960,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2989,12 +2970,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,10 +2997,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124987740</v>
+        <v>124981403</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3037,34 +3013,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587191</v>
+        <v>587070</v>
       </c>
       <c r="R22" t="n">
-        <v>6938140</v>
+        <v>6938040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3096,7 +3077,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3106,7 +3087,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,22 +3107,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124987889</v>
+        <v>124981684</v>
       </c>
       <c r="B23" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3149,34 +3135,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587214</v>
+        <v>587057</v>
       </c>
       <c r="R23" t="n">
-        <v>6938134</v>
+        <v>6938054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3208,7 +3198,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3218,7 +3208,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,22 +3223,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124987521</v>
+        <v>124988185</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3261,21 +3251,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3285,10 +3275,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587127</v>
+        <v>587197</v>
       </c>
       <c r="R24" t="n">
-        <v>6938166</v>
+        <v>6938055</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,7 +3310,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,7 +3320,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3357,10 +3347,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124988050</v>
+        <v>124985796</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3373,21 +3363,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3397,7 +3387,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587221</v>
+        <v>587080</v>
       </c>
       <c r="R25" t="n">
         <v>6938107</v>
@@ -3432,7 +3422,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3442,7 +3432,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3469,10 +3459,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124988415</v>
+        <v>124988323</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3485,34 +3475,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587161</v>
+        <v>587174</v>
       </c>
       <c r="R26" t="n">
-        <v>6938018</v>
+        <v>6938028</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3544,7 +3539,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3554,7 +3549,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124982589</v>
+        <v>124981815</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3593,38 +3593,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586904</v>
+        <v>587032</v>
       </c>
       <c r="R27" t="n">
-        <v>6938096</v>
+        <v>6938083</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,7 +3660,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3666,7 +3670,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,22 +3685,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124989421</v>
+        <v>124985568</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3709,34 +3713,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587147</v>
+        <v>587027</v>
       </c>
       <c r="R28" t="n">
-        <v>6937978</v>
+        <v>6938028</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3768,7 +3777,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3778,7 +3787,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3793,19 +3807,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124987817</v>
+        <v>124989421</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3845,10 +3859,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587218</v>
+        <v>587147</v>
       </c>
       <c r="R29" t="n">
-        <v>6938125</v>
+        <v>6937978</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3880,7 +3894,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3890,7 +3904,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3917,7 +3931,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124982787</v>
+        <v>124981283</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3953,19 +3967,19 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586882</v>
+        <v>587053</v>
       </c>
       <c r="R30" t="n">
-        <v>6938074</v>
+        <v>6938038</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3997,7 +4011,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4007,7 +4021,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4027,22 +4041,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124989520</v>
+        <v>124987889</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4051,25 +4065,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4079,10 +4093,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587123</v>
+        <v>587214</v>
       </c>
       <c r="R31" t="n">
-        <v>6937980</v>
+        <v>6938134</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4114,7 +4128,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4124,7 +4138,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4139,22 +4153,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124982748</v>
+        <v>124982289</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4167,34 +4181,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586911</v>
+        <v>586956</v>
       </c>
       <c r="R32" t="n">
-        <v>6938088</v>
+        <v>6938114</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4226,7 +4245,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4236,7 +4255,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4251,19 +4275,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124983267</v>
+        <v>124983114</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4303,10 +4327,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586804</v>
+        <v>586836</v>
       </c>
       <c r="R33" t="n">
-        <v>6938078</v>
+        <v>6938079</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4338,7 +4362,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4348,7 +4372,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4363,22 +4387,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124988491</v>
+        <v>124988918</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4387,35 +4411,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4424,10 +4444,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587193</v>
+        <v>587221</v>
       </c>
       <c r="R34" t="n">
-        <v>6938003</v>
+        <v>6937950</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4459,7 +4479,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4469,7 +4489,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4484,22 +4509,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124983653</v>
+        <v>124982567</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4512,39 +4537,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586814</v>
+        <v>586907</v>
       </c>
       <c r="R35" t="n">
-        <v>6938043</v>
+        <v>6938087</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4576,7 +4596,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4586,12 +4606,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4606,22 +4621,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124988969</v>
+        <v>124984652</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4634,39 +4649,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587225</v>
+        <v>586891</v>
       </c>
       <c r="R36" t="n">
-        <v>6937951</v>
+        <v>6937995</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4698,7 +4708,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4708,12 +4718,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4740,7 +4745,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124988529</v>
+        <v>124988050</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4780,10 +4785,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587145</v>
+        <v>587221</v>
       </c>
       <c r="R37" t="n">
-        <v>6938003</v>
+        <v>6938107</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4815,7 +4820,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4825,7 +4830,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4852,10 +4857,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124982170</v>
+        <v>124989520</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4868,39 +4873,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586964</v>
+        <v>587123</v>
       </c>
       <c r="R38" t="n">
-        <v>6938109</v>
+        <v>6937980</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4942,12 +4942,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4962,22 +4957,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124987424</v>
+        <v>124988270</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4990,39 +4985,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587103</v>
+        <v>587190</v>
       </c>
       <c r="R39" t="n">
-        <v>6938206</v>
+        <v>6938036</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5054,7 +5044,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5064,7 +5054,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5079,19 +5069,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124987318</v>
+        <v>124987521</v>
       </c>
       <c r="B40" t="n">
         <v>79891</v>
@@ -5131,10 +5121,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587102</v>
+        <v>587127</v>
       </c>
       <c r="R40" t="n">
-        <v>6938235</v>
+        <v>6938166</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5166,7 +5156,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5176,7 +5166,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5203,7 +5193,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124987383</v>
+        <v>124987066</v>
       </c>
       <c r="B41" t="n">
         <v>79891</v>
@@ -5243,10 +5233,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587108</v>
+        <v>587081</v>
       </c>
       <c r="R41" t="n">
-        <v>6938215</v>
+        <v>6938219</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5278,7 +5268,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5288,7 +5278,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5303,22 +5293,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124981660</v>
+        <v>124987125</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5331,21 +5321,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5355,10 +5345,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587048</v>
+        <v>587084</v>
       </c>
       <c r="R42" t="n">
-        <v>6938056</v>
+        <v>6938203</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5390,7 +5380,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5400,7 +5390,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,10 +5417,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124982567</v>
+        <v>124981756</v>
       </c>
       <c r="B43" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,37 +5433,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586907</v>
+        <v>587045</v>
       </c>
       <c r="R43" t="n">
-        <v>6938087</v>
+        <v>6938068</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5502,7 +5497,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5512,7 +5507,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5527,22 +5527,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124986178</v>
+        <v>124986659</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5555,21 +5555,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587008</v>
+        <v>587032</v>
       </c>
       <c r="R44" t="n">
-        <v>6938211</v>
+        <v>6938236</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5651,10 +5651,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124982289</v>
+        <v>124987740</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5667,39 +5667,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586956</v>
+        <v>587191</v>
       </c>
       <c r="R45" t="n">
-        <v>6938114</v>
+        <v>6938140</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5731,7 +5726,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5741,12 +5736,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5761,19 +5751,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124985568</v>
+        <v>124982787</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5809,7 +5799,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5818,10 +5808,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587027</v>
+        <v>586882</v>
       </c>
       <c r="R46" t="n">
-        <v>6938028</v>
+        <v>6938074</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5853,7 +5843,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5863,12 +5853,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5895,10 +5885,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124981756</v>
+        <v>124981660</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5911,42 +5901,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587045</v>
+        <v>587048</v>
       </c>
       <c r="R47" t="n">
-        <v>6938068</v>
+        <v>6938056</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5975,7 +5960,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5985,12 +5970,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6005,22 +5985,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124981283</v>
+        <v>124982748</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6033,39 +6013,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587053</v>
+        <v>586911</v>
       </c>
       <c r="R48" t="n">
-        <v>6938038</v>
+        <v>6938088</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6097,7 +6072,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6107,12 +6082,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6139,10 +6109,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124986918</v>
+        <v>124983653</v>
       </c>
       <c r="B49" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6155,34 +6125,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587054</v>
+        <v>586814</v>
       </c>
       <c r="R49" t="n">
-        <v>6938245</v>
+        <v>6938043</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6214,7 +6189,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6224,7 +6199,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6239,22 +6219,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124982003</v>
+        <v>124986178</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6267,21 +6247,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6291,10 +6271,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587036</v>
+        <v>587008</v>
       </c>
       <c r="R50" t="n">
-        <v>6938128</v>
+        <v>6938211</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6326,7 +6306,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6336,7 +6316,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6363,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124983114</v>
+        <v>124988969</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6379,34 +6359,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586836</v>
+        <v>587225</v>
       </c>
       <c r="R51" t="n">
-        <v>6938079</v>
+        <v>6937951</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6438,7 +6423,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6448,7 +6433,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6475,10 +6465,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124986659</v>
+        <v>124988914</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,34 +6481,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587032</v>
+        <v>587193</v>
       </c>
       <c r="R52" t="n">
-        <v>6938236</v>
+        <v>6937956</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6545,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6555,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6575,12 +6575,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -1615,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124987383</v>
+        <v>124983563</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,34 +1631,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587108</v>
+        <v>586799</v>
       </c>
       <c r="R10" t="n">
-        <v>6938215</v>
+        <v>6938055</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1705,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124988529</v>
+        <v>124987383</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,21 +1753,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1767,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587145</v>
+        <v>587108</v>
       </c>
       <c r="R11" t="n">
-        <v>6938003</v>
+        <v>6938215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124983563</v>
+        <v>124988529</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,39 +1865,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586799</v>
+        <v>587145</v>
       </c>
       <c r="R12" t="n">
-        <v>6938055</v>
+        <v>6938003</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,12 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124982589</v>
+        <v>124981403</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2789,34 +2789,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586904</v>
+        <v>587070</v>
       </c>
       <c r="R20" t="n">
-        <v>6938096</v>
+        <v>6938040</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2848,7 +2853,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2858,7 +2863,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,10 +2895,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124981850</v>
+        <v>124982589</v>
       </c>
       <c r="B21" t="n">
-        <v>98122</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2897,38 +2907,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587051</v>
+        <v>586904</v>
       </c>
       <c r="R21" t="n">
-        <v>6938101</v>
+        <v>6938096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2960,7 +2970,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2970,7 +2980,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,22 +2995,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124981403</v>
+        <v>124981850</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,43 +3019,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587070</v>
+        <v>587051</v>
       </c>
       <c r="R22" t="n">
-        <v>6938040</v>
+        <v>6938101</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,7 +3082,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3087,12 +3092,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,22 +3107,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124981684</v>
+        <v>124988185</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3131,42 +3131,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587057</v>
+        <v>587197</v>
       </c>
       <c r="R23" t="n">
-        <v>6938054</v>
+        <v>6938055</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3198,7 +3194,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3208,7 +3204,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3235,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124988185</v>
+        <v>124985796</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3251,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3275,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587197</v>
+        <v>587080</v>
       </c>
       <c r="R24" t="n">
-        <v>6938055</v>
+        <v>6938107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3310,7 +3306,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3320,7 +3316,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,10 +3343,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124985796</v>
+        <v>124988323</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3363,34 +3359,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587080</v>
+        <v>587174</v>
       </c>
       <c r="R25" t="n">
-        <v>6938107</v>
+        <v>6938028</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3432,7 +3433,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,10 +3465,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124988323</v>
+        <v>124981815</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3471,31 +3477,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3504,10 +3509,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587174</v>
+        <v>587032</v>
       </c>
       <c r="R26" t="n">
-        <v>6938028</v>
+        <v>6938083</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,7 +3544,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3549,12 +3554,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3581,7 +3581,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124981815</v>
+        <v>124981684</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587032</v>
+        <v>587057</v>
       </c>
       <c r="R27" t="n">
-        <v>6938083</v>
+        <v>6938054</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,10 +3697,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124985568</v>
+        <v>124989421</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3713,39 +3713,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587027</v>
+        <v>587147</v>
       </c>
       <c r="R28" t="n">
-        <v>6938028</v>
+        <v>6937978</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3777,7 +3772,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3787,12 +3782,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,22 +3797,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124989421</v>
+        <v>124985568</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3835,34 +3825,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587147</v>
+        <v>587027</v>
       </c>
       <c r="R29" t="n">
-        <v>6937978</v>
+        <v>6938028</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3894,7 +3889,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3904,7 +3899,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,12 +3919,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4165,10 +4165,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124982289</v>
+        <v>124983114</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4181,39 +4181,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586956</v>
+        <v>586836</v>
       </c>
       <c r="R32" t="n">
-        <v>6938114</v>
+        <v>6938079</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4245,7 +4240,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4255,12 +4250,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4275,22 +4265,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124983114</v>
+        <v>124982289</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4303,34 +4293,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586836</v>
+        <v>586956</v>
       </c>
       <c r="R33" t="n">
-        <v>6938079</v>
+        <v>6938114</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4362,7 +4357,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4372,7 +4367,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4387,12 +4387,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124989520</v>
+        <v>124981756</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4873,37 +4873,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587123</v>
+        <v>587045</v>
       </c>
       <c r="R38" t="n">
-        <v>6937980</v>
+        <v>6938068</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4932,7 +4937,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4942,7 +4947,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4957,19 +4967,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124988270</v>
+        <v>124989520</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -5009,10 +5019,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587190</v>
+        <v>587123</v>
       </c>
       <c r="R39" t="n">
-        <v>6938036</v>
+        <v>6937980</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5044,7 +5054,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5054,7 +5064,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5081,10 +5091,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124987521</v>
+        <v>124988270</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5097,21 +5107,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5121,10 +5131,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587127</v>
+        <v>587190</v>
       </c>
       <c r="R40" t="n">
-        <v>6938166</v>
+        <v>6938036</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5156,7 +5166,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5166,7 +5176,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5193,7 +5203,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124987066</v>
+        <v>124987521</v>
       </c>
       <c r="B41" t="n">
         <v>79891</v>
@@ -5233,10 +5243,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587081</v>
+        <v>587127</v>
       </c>
       <c r="R41" t="n">
-        <v>6938219</v>
+        <v>6938166</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5268,7 +5278,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5278,7 +5288,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,19 +5303,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124987125</v>
+        <v>124987066</v>
       </c>
       <c r="B42" t="n">
         <v>79891</v>
@@ -5345,10 +5355,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587084</v>
+        <v>587081</v>
       </c>
       <c r="R42" t="n">
-        <v>6938203</v>
+        <v>6938219</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5380,7 +5390,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5390,7 +5400,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5405,22 +5415,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124981756</v>
+        <v>124987125</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5433,42 +5443,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587045</v>
+        <v>587084</v>
       </c>
       <c r="R43" t="n">
-        <v>6938068</v>
+        <v>6938203</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5497,7 +5502,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5507,12 +5512,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5527,12 +5527,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124988491</v>
+        <v>124981403</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587193</v>
+        <v>587070</v>
       </c>
       <c r="R2" t="n">
-        <v>6938003</v>
+        <v>6938040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987817</v>
+        <v>124989520</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587218</v>
+        <v>587123</v>
       </c>
       <c r="R3" t="n">
-        <v>6938125</v>
+        <v>6937980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124982170</v>
+        <v>124987066</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586964</v>
+        <v>587081</v>
       </c>
       <c r="R4" t="n">
-        <v>6938109</v>
+        <v>6938219</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987424</v>
+        <v>124988050</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587103</v>
+        <v>587221</v>
       </c>
       <c r="R5" t="n">
-        <v>6938206</v>
+        <v>6938107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124985931</v>
+        <v>124983267</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587058</v>
+        <v>586804</v>
       </c>
       <c r="R6" t="n">
-        <v>6938138</v>
+        <v>6938078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988641</v>
+        <v>124989553</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,31 +1257,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,7 +1294,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587123</v>
+        <v>587128</v>
       </c>
       <c r="R7" t="n">
         <v>6937990</v>
@@ -1349,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124986918</v>
+        <v>124986503</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,37 +1382,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587054</v>
+        <v>587003</v>
       </c>
       <c r="R8" t="n">
-        <v>6938245</v>
+        <v>6938230</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1476,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983267</v>
+        <v>124985796</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,34 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586804</v>
+        <v>587080</v>
       </c>
       <c r="R9" t="n">
-        <v>6938078</v>
+        <v>6938107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,19 +1588,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124983563</v>
+        <v>124982289</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1660,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586799</v>
+        <v>586956</v>
       </c>
       <c r="R10" t="n">
-        <v>6938055</v>
+        <v>6938114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,12 +1690,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,19 +1710,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987383</v>
+        <v>124986538</v>
       </c>
       <c r="B11" t="n">
         <v>79891</v>
@@ -1773,14 +1758,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587108</v>
+        <v>587003</v>
       </c>
       <c r="R11" t="n">
-        <v>6938215</v>
+        <v>6938235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,12 +1822,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1961,7 +1946,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124988415</v>
+        <v>124983114</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1997,14 +1982,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587161</v>
+        <v>586836</v>
       </c>
       <c r="R13" t="n">
-        <v>6938018</v>
+        <v>6938079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2036,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987318</v>
+        <v>124988914</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,34 +2074,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587102</v>
+        <v>587193</v>
       </c>
       <c r="R14" t="n">
-        <v>6938235</v>
+        <v>6937956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2148,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,19 +2168,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124982003</v>
+        <v>124987383</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2225,10 +2220,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587036</v>
+        <v>587108</v>
       </c>
       <c r="R15" t="n">
-        <v>6938128</v>
+        <v>6938215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2292,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124990166</v>
+        <v>124987740</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,47 +2304,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587097</v>
+        <v>587191</v>
       </c>
       <c r="R16" t="n">
-        <v>6937989</v>
+        <v>6938140</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2377,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,22 +2392,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124989553</v>
+        <v>124988969</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,35 +2416,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2467,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587128</v>
+        <v>587225</v>
       </c>
       <c r="R17" t="n">
-        <v>6937990</v>
+        <v>6937951</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2502,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2512,7 +2494,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,22 +2514,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124986538</v>
+        <v>124988270</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2555,34 +2542,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587003</v>
+        <v>587190</v>
       </c>
       <c r="R18" t="n">
-        <v>6938235</v>
+        <v>6938036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2624,7 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,22 +2626,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124986503</v>
+        <v>124989421</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,47 +2654,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587003</v>
+        <v>587147</v>
       </c>
       <c r="R19" t="n">
-        <v>6938230</v>
+        <v>6937978</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2736,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2746,7 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,22 +2738,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124981403</v>
+        <v>124987817</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2789,39 +2766,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587070</v>
+        <v>587218</v>
       </c>
       <c r="R20" t="n">
-        <v>6938040</v>
+        <v>6938125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2853,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2863,12 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,22 +2850,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124982589</v>
+        <v>124987521</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2911,34 +2878,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586904</v>
+        <v>587127</v>
       </c>
       <c r="R21" t="n">
-        <v>6938096</v>
+        <v>6938166</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2970,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2980,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,22 +2962,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124981850</v>
+        <v>124987318</v>
       </c>
       <c r="B22" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,25 +2986,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3047,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587051</v>
+        <v>587102</v>
       </c>
       <c r="R22" t="n">
-        <v>6938101</v>
+        <v>6938235</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3082,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3092,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124988185</v>
+        <v>124988491</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3131,38 +3098,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587197</v>
+        <v>587193</v>
       </c>
       <c r="R23" t="n">
-        <v>6938055</v>
+        <v>6938003</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3194,7 +3170,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3204,7 +3180,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,22 +3195,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124985796</v>
+        <v>124986918</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,21 +3223,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587080</v>
+        <v>587054</v>
       </c>
       <c r="R24" t="n">
-        <v>6938107</v>
+        <v>6938245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3306,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3316,7 +3292,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3343,7 +3319,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124988323</v>
+        <v>124982170</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3379,19 +3355,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587174</v>
+        <v>586964</v>
       </c>
       <c r="R25" t="n">
-        <v>6938028</v>
+        <v>6938109</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3423,7 +3399,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,7 +3409,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3453,22 +3429,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124981815</v>
+        <v>124988323</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3477,30 +3453,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3509,10 +3486,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587032</v>
+        <v>587174</v>
       </c>
       <c r="R26" t="n">
-        <v>6938083</v>
+        <v>6938028</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3544,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3554,7 +3531,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3581,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124981684</v>
+        <v>124988918</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3593,30 +3575,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3625,10 +3608,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587057</v>
+        <v>587221</v>
       </c>
       <c r="R27" t="n">
-        <v>6938054</v>
+        <v>6937950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3660,7 +3643,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3670,7 +3653,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,7 +3685,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124989421</v>
+        <v>124982748</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3733,14 +3721,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587147</v>
+        <v>586911</v>
       </c>
       <c r="R28" t="n">
-        <v>6937978</v>
+        <v>6938088</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3772,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3782,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3809,7 +3797,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124985568</v>
+        <v>124983563</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3850,14 +3838,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587027</v>
+        <v>586799</v>
       </c>
       <c r="R29" t="n">
-        <v>6938028</v>
+        <v>6938055</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3889,7 +3877,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3899,12 +3887,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,19 +3907,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124981283</v>
+        <v>124988641</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3976,10 +3964,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587053</v>
+        <v>587123</v>
       </c>
       <c r="R30" t="n">
-        <v>6938038</v>
+        <v>6937990</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4011,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4021,7 +4009,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4053,10 +4041,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124987889</v>
+        <v>124987125</v>
       </c>
       <c r="B31" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4065,25 +4053,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4093,10 +4081,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587214</v>
+        <v>587084</v>
       </c>
       <c r="R31" t="n">
-        <v>6938134</v>
+        <v>6938203</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4128,7 +4116,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4138,7 +4126,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,22 +4141,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124983114</v>
+        <v>124981684</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4177,38 +4165,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586836</v>
+        <v>587057</v>
       </c>
       <c r="R32" t="n">
-        <v>6938079</v>
+        <v>6938054</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,7 +4232,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4250,7 +4242,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4277,10 +4269,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124982289</v>
+        <v>124981660</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4293,39 +4285,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586956</v>
+        <v>587048</v>
       </c>
       <c r="R33" t="n">
-        <v>6938114</v>
+        <v>6938056</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4357,7 +4344,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4367,12 +4354,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4387,22 +4369,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124988918</v>
+        <v>124988185</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4415,39 +4397,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587221</v>
+        <v>587197</v>
       </c>
       <c r="R34" t="n">
-        <v>6937950</v>
+        <v>6938055</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4479,7 +4456,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4489,12 +4466,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4521,10 +4493,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124982567</v>
+        <v>124986178</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4537,34 +4509,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586907</v>
+        <v>587008</v>
       </c>
       <c r="R35" t="n">
-        <v>6938087</v>
+        <v>6938211</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4596,7 +4568,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4606,7 +4578,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4745,10 +4717,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124988050</v>
+        <v>124985931</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4761,34 +4733,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587221</v>
+        <v>587058</v>
       </c>
       <c r="R37" t="n">
-        <v>6938107</v>
+        <v>6938138</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4820,7 +4797,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4830,7 +4807,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4857,7 +4839,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124981756</v>
+        <v>124983653</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4893,22 +4875,22 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587045</v>
+        <v>586814</v>
       </c>
       <c r="R38" t="n">
-        <v>6938068</v>
+        <v>6938043</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4937,7 +4919,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4947,12 +4929,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4979,10 +4961,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124989520</v>
+        <v>124982589</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4995,34 +4977,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587123</v>
+        <v>586904</v>
       </c>
       <c r="R39" t="n">
-        <v>6937980</v>
+        <v>6938096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5054,7 +5036,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5064,7 +5046,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5079,19 +5061,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124988270</v>
+        <v>124988415</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -5131,10 +5113,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587190</v>
+        <v>587161</v>
       </c>
       <c r="R40" t="n">
-        <v>6938036</v>
+        <v>6938018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5166,7 +5148,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5176,7 +5158,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5203,10 +5185,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124987521</v>
+        <v>124981756</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5219,37 +5201,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587127</v>
+        <v>587045</v>
       </c>
       <c r="R41" t="n">
-        <v>6938166</v>
+        <v>6938068</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5278,7 +5265,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5288,7 +5275,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5303,22 +5295,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124987066</v>
+        <v>124982787</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5331,34 +5323,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587081</v>
+        <v>586882</v>
       </c>
       <c r="R42" t="n">
-        <v>6938219</v>
+        <v>6938074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5390,7 +5387,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5400,7 +5397,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5427,7 +5429,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124987125</v>
+        <v>124982003</v>
       </c>
       <c r="B43" t="n">
         <v>79891</v>
@@ -5467,10 +5469,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587084</v>
+        <v>587036</v>
       </c>
       <c r="R43" t="n">
-        <v>6938203</v>
+        <v>6938128</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5502,7 +5504,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5512,7 +5514,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5539,10 +5541,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124986659</v>
+        <v>124987424</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5555,34 +5557,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587032</v>
+        <v>587103</v>
       </c>
       <c r="R44" t="n">
-        <v>6938236</v>
+        <v>6938206</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5614,7 +5621,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5624,7 +5631,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5639,22 +5646,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124987740</v>
+        <v>124985568</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5667,34 +5674,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587191</v>
+        <v>587027</v>
       </c>
       <c r="R45" t="n">
-        <v>6938140</v>
+        <v>6938028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5726,7 +5738,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5736,7 +5748,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5751,19 +5768,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124982787</v>
+        <v>124981283</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5799,19 +5816,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586882</v>
+        <v>587053</v>
       </c>
       <c r="R46" t="n">
-        <v>6938074</v>
+        <v>6938038</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5843,7 +5860,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5853,7 +5870,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5873,22 +5890,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124981660</v>
+        <v>124986659</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5901,21 +5918,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5925,10 +5942,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587048</v>
+        <v>587032</v>
       </c>
       <c r="R47" t="n">
-        <v>6938056</v>
+        <v>6938236</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5960,7 +5977,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5970,7 +5987,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5997,10 +6014,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124982748</v>
+        <v>124981815</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6009,38 +6026,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586911</v>
+        <v>587032</v>
       </c>
       <c r="R48" t="n">
-        <v>6938088</v>
+        <v>6938083</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6072,7 +6093,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6082,7 +6103,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6109,10 +6130,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124983653</v>
+        <v>124982567</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6125,39 +6146,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586814</v>
+        <v>586907</v>
       </c>
       <c r="R49" t="n">
-        <v>6938043</v>
+        <v>6938087</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6189,7 +6205,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6199,12 +6215,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6219,22 +6230,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124986178</v>
+        <v>124987889</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6243,25 +6254,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6271,10 +6282,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587008</v>
+        <v>587214</v>
       </c>
       <c r="R50" t="n">
-        <v>6938211</v>
+        <v>6938134</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6306,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6316,7 +6327,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6331,22 +6342,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124988969</v>
+        <v>124990166</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6355,31 +6366,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6388,10 +6403,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587225</v>
+        <v>587097</v>
       </c>
       <c r="R51" t="n">
-        <v>6937951</v>
+        <v>6937989</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6423,7 +6438,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6433,12 +6448,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6453,22 +6463,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124988914</v>
+        <v>124981850</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>98122</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6477,43 +6487,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587193</v>
+        <v>587051</v>
       </c>
       <c r="R52" t="n">
-        <v>6937956</v>
+        <v>6938101</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6545,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6555,12 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6575,12 +6575,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -1600,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124982289</v>
+        <v>124986538</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1616,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586956</v>
+        <v>587003</v>
       </c>
       <c r="R10" t="n">
-        <v>6938114</v>
+        <v>6938235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124986538</v>
+        <v>124988529</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,34 +1728,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587003</v>
+        <v>587145</v>
       </c>
       <c r="R11" t="n">
-        <v>6938235</v>
+        <v>6938003</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,22 +1812,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124988529</v>
+        <v>124982289</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,34 +1840,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587145</v>
+        <v>586956</v>
       </c>
       <c r="R12" t="n">
-        <v>6938003</v>
+        <v>6938114</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,12 +1934,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981403</v>
+        <v>124987521</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587070</v>
+        <v>587127</v>
       </c>
       <c r="R2" t="n">
-        <v>6938040</v>
+        <v>6938166</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124989520</v>
+        <v>124986918</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587123</v>
+        <v>587054</v>
       </c>
       <c r="R3" t="n">
-        <v>6937980</v>
+        <v>6938245</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987066</v>
+        <v>124986178</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587081</v>
+        <v>587008</v>
       </c>
       <c r="R4" t="n">
-        <v>6938219</v>
+        <v>6938211</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988050</v>
+        <v>124982003</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587221</v>
+        <v>587036</v>
       </c>
       <c r="R5" t="n">
-        <v>6938107</v>
+        <v>6938128</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124983267</v>
+        <v>124987318</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586804</v>
+        <v>587102</v>
       </c>
       <c r="R6" t="n">
-        <v>6938078</v>
+        <v>6938235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124989553</v>
+        <v>124983114</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,47 +1247,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587128</v>
+        <v>586836</v>
       </c>
       <c r="R7" t="n">
-        <v>6937990</v>
+        <v>6938079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,19 +1335,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124986503</v>
+        <v>124988969</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1400,29 +1381,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587003</v>
+        <v>587225</v>
       </c>
       <c r="R8" t="n">
-        <v>6938230</v>
+        <v>6937951</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124985796</v>
+        <v>124983267</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1485,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587080</v>
+        <v>586804</v>
       </c>
       <c r="R9" t="n">
-        <v>6938107</v>
+        <v>6938078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124986538</v>
+        <v>124988529</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,34 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587003</v>
+        <v>587145</v>
       </c>
       <c r="R10" t="n">
-        <v>6938235</v>
+        <v>6938003</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124988529</v>
+        <v>124983563</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1709,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587145</v>
+        <v>586799</v>
       </c>
       <c r="R11" t="n">
-        <v>6938003</v>
+        <v>6938055</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1783,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124982289</v>
+        <v>124988323</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1865,14 +1856,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586956</v>
+        <v>587174</v>
       </c>
       <c r="R12" t="n">
-        <v>6938114</v>
+        <v>6938028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1905,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,22 +1925,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124983114</v>
+        <v>124987125</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,34 +1953,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586836</v>
+        <v>587084</v>
       </c>
       <c r="R13" t="n">
-        <v>6938079</v>
+        <v>6938203</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988914</v>
+        <v>124987817</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,39 +2065,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587193</v>
+        <v>587218</v>
       </c>
       <c r="R14" t="n">
-        <v>6937956</v>
+        <v>6938125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,12 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,19 +2149,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987383</v>
+        <v>124987740</v>
       </c>
       <c r="B15" t="n">
         <v>79891</v>
@@ -2220,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587108</v>
+        <v>587191</v>
       </c>
       <c r="R15" t="n">
-        <v>6938215</v>
+        <v>6938140</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124987740</v>
+        <v>124989520</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,21 +2289,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2313,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587191</v>
+        <v>587123</v>
       </c>
       <c r="R16" t="n">
-        <v>6938140</v>
+        <v>6937980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988969</v>
+        <v>124986538</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,39 +2401,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587225</v>
+        <v>587003</v>
       </c>
       <c r="R17" t="n">
-        <v>6937951</v>
+        <v>6938235</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,12 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,22 +2485,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988270</v>
+        <v>124988914</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,34 +2513,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587190</v>
+        <v>587193</v>
       </c>
       <c r="R18" t="n">
-        <v>6938036</v>
+        <v>6937956</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2587,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,22 +2607,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124989421</v>
+        <v>124981283</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,34 +2635,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587147</v>
+        <v>587053</v>
       </c>
       <c r="R19" t="n">
-        <v>6937978</v>
+        <v>6938038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2741,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124987817</v>
+        <v>124982567</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,34 +2757,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587218</v>
+        <v>586907</v>
       </c>
       <c r="R20" t="n">
-        <v>6938125</v>
+        <v>6938087</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2816,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2826,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124987521</v>
+        <v>124982748</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2869,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587127</v>
+        <v>586911</v>
       </c>
       <c r="R21" t="n">
-        <v>6938166</v>
+        <v>6938088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2938,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124987318</v>
+        <v>124988491</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,38 +2977,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587102</v>
+        <v>587193</v>
       </c>
       <c r="R22" t="n">
-        <v>6938235</v>
+        <v>6938003</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,19 +3074,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124988491</v>
+        <v>124989553</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587193</v>
+        <v>587128</v>
       </c>
       <c r="R23" t="n">
-        <v>6938003</v>
+        <v>6937990</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3207,10 +3207,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124986918</v>
+        <v>124988185</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3223,21 +3223,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587054</v>
+        <v>587197</v>
       </c>
       <c r="R24" t="n">
-        <v>6938245</v>
+        <v>6938055</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3319,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124982170</v>
+        <v>124988050</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,39 +3335,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586964</v>
+        <v>587221</v>
       </c>
       <c r="R25" t="n">
-        <v>6938109</v>
+        <v>6938107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3409,12 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3429,19 +3419,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124988323</v>
+        <v>124982170</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3477,19 +3467,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587174</v>
+        <v>586964</v>
       </c>
       <c r="R26" t="n">
-        <v>6938028</v>
+        <v>6938109</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,7 +3511,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3521,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3551,22 +3541,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124988918</v>
+        <v>124990166</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,31 +3565,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3608,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587221</v>
+        <v>587097</v>
       </c>
       <c r="R27" t="n">
-        <v>6937950</v>
+        <v>6937989</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3643,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3653,12 +3647,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,19 +3662,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124982748</v>
+        <v>124988270</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3721,14 +3710,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586911</v>
+        <v>587190</v>
       </c>
       <c r="R28" t="n">
-        <v>6938088</v>
+        <v>6938036</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3749,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3759,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,10 +3786,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124983563</v>
+        <v>124987889</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,43 +3798,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586799</v>
+        <v>587214</v>
       </c>
       <c r="R29" t="n">
-        <v>6938055</v>
+        <v>6938134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3877,7 +3861,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3887,12 +3871,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,22 +3886,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124988641</v>
+        <v>124987383</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3935,39 +3914,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587123</v>
+        <v>587108</v>
       </c>
       <c r="R30" t="n">
-        <v>6937990</v>
+        <v>6938215</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3999,7 +3973,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +3983,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4041,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124987125</v>
+        <v>124986503</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4057,37 +4026,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587084</v>
+        <v>587003</v>
       </c>
       <c r="R31" t="n">
-        <v>6938203</v>
+        <v>6938230</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4116,7 +4095,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4126,7 +4105,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,19 +4120,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124981684</v>
+        <v>124981815</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4188,7 +4167,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4197,10 +4176,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587057</v>
+        <v>587032</v>
       </c>
       <c r="R32" t="n">
-        <v>6938054</v>
+        <v>6938083</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4232,7 +4211,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4242,7 +4221,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4269,10 +4248,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124981660</v>
+        <v>124981850</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98122</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4281,25 +4260,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4309,10 +4288,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587048</v>
+        <v>587051</v>
       </c>
       <c r="R33" t="n">
-        <v>6938056</v>
+        <v>6938101</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4344,7 +4323,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4354,7 +4333,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4381,10 +4360,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124988185</v>
+        <v>124987424</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4397,34 +4376,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587197</v>
+        <v>587103</v>
       </c>
       <c r="R34" t="n">
-        <v>6938055</v>
+        <v>6938206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4456,7 +4440,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4466,7 +4450,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4481,22 +4465,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124986178</v>
+        <v>124985931</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4509,34 +4493,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587008</v>
+        <v>587058</v>
       </c>
       <c r="R35" t="n">
-        <v>6938211</v>
+        <v>6938138</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4568,7 +4557,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4578,7 +4567,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4605,7 +4599,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124984652</v>
+        <v>124981660</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4641,14 +4635,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586891</v>
+        <v>587048</v>
       </c>
       <c r="R36" t="n">
-        <v>6937995</v>
+        <v>6938056</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4680,7 +4674,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4690,7 +4684,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4717,7 +4711,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124985931</v>
+        <v>124985568</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4753,19 +4747,19 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587058</v>
+        <v>587027</v>
       </c>
       <c r="R37" t="n">
-        <v>6938138</v>
+        <v>6938028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4797,7 +4791,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4807,12 +4801,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4827,19 +4821,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124983653</v>
+        <v>124982289</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4880,14 +4874,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586814</v>
+        <v>586956</v>
       </c>
       <c r="R38" t="n">
-        <v>6938043</v>
+        <v>6938114</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4919,7 +4913,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4929,12 +4923,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4961,10 +4955,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124982589</v>
+        <v>124981403</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4977,34 +4971,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586904</v>
+        <v>587070</v>
       </c>
       <c r="R39" t="n">
-        <v>6938096</v>
+        <v>6938040</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5036,7 +5035,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5046,7 +5045,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5073,10 +5077,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124988415</v>
+        <v>124988918</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5089,34 +5093,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587161</v>
+        <v>587221</v>
       </c>
       <c r="R40" t="n">
-        <v>6938018</v>
+        <v>6937950</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5148,7 +5157,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5158,7 +5167,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5185,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124981756</v>
+        <v>124989421</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5201,42 +5215,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587045</v>
+        <v>587147</v>
       </c>
       <c r="R41" t="n">
-        <v>6938068</v>
+        <v>6937978</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5265,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5275,12 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5295,22 +5299,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124982787</v>
+        <v>124988415</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5323,39 +5327,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586882</v>
+        <v>587161</v>
       </c>
       <c r="R42" t="n">
-        <v>6938074</v>
+        <v>6938018</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5387,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5397,12 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5417,19 +5411,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124982003</v>
+        <v>124987066</v>
       </c>
       <c r="B43" t="n">
         <v>79891</v>
@@ -5469,10 +5463,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587036</v>
+        <v>587081</v>
       </c>
       <c r="R43" t="n">
-        <v>6938128</v>
+        <v>6938219</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5504,7 +5498,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5514,7 +5508,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,22 +5523,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124987424</v>
+        <v>124982589</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5557,39 +5551,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587103</v>
+        <v>586904</v>
       </c>
       <c r="R44" t="n">
-        <v>6938206</v>
+        <v>6938096</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5621,7 +5610,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5631,7 +5620,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5658,10 +5647,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124985568</v>
+        <v>124986659</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5674,39 +5663,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587027</v>
+        <v>587032</v>
       </c>
       <c r="R45" t="n">
-        <v>6938028</v>
+        <v>6938236</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5738,7 +5722,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5748,12 +5732,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5768,19 +5747,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124981283</v>
+        <v>124981756</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5816,7 +5795,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5825,13 +5804,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587053</v>
+        <v>587045</v>
       </c>
       <c r="R46" t="n">
-        <v>6938038</v>
+        <v>6938068</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5860,7 +5839,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5870,12 +5849,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5890,19 +5869,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124986659</v>
+        <v>124985796</v>
       </c>
       <c r="B47" t="n">
         <v>79891</v>
@@ -5942,10 +5921,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587032</v>
+        <v>587080</v>
       </c>
       <c r="R47" t="n">
-        <v>6938236</v>
+        <v>6938107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5977,7 +5956,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5987,7 +5966,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6014,10 +5993,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124981815</v>
+        <v>124988641</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6026,30 +6005,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6058,10 +6038,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587032</v>
+        <v>587123</v>
       </c>
       <c r="R48" t="n">
-        <v>6938083</v>
+        <v>6937990</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6093,7 +6073,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6103,7 +6083,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6130,10 +6115,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124982567</v>
+        <v>124981684</v>
       </c>
       <c r="B49" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6142,38 +6127,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586907</v>
+        <v>587057</v>
       </c>
       <c r="R49" t="n">
-        <v>6938087</v>
+        <v>6938054</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6205,7 +6194,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6215,7 +6204,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6242,10 +6231,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124987889</v>
+        <v>124984652</v>
       </c>
       <c r="B50" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6254,38 +6243,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587214</v>
+        <v>586891</v>
       </c>
       <c r="R50" t="n">
-        <v>6938134</v>
+        <v>6937995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6317,7 +6306,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6316,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6342,22 +6331,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124990166</v>
+        <v>124982787</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6366,47 +6355,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587097</v>
+        <v>586882</v>
       </c>
       <c r="R51" t="n">
-        <v>6937989</v>
+        <v>6938074</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6438,7 +6423,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6448,7 +6433,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6475,10 +6465,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124981850</v>
+        <v>124983653</v>
       </c>
       <c r="B52" t="n">
-        <v>98122</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6487,38 +6477,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587051</v>
+        <v>586814</v>
       </c>
       <c r="R52" t="n">
-        <v>6938101</v>
+        <v>6938043</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6545,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6555,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6575,12 +6575,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987521</v>
+        <v>124982787</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587127</v>
+        <v>586882</v>
       </c>
       <c r="R2" t="n">
-        <v>6938166</v>
+        <v>6938074</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124986918</v>
+        <v>124988641</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587054</v>
+        <v>587123</v>
       </c>
       <c r="R3" t="n">
-        <v>6938245</v>
+        <v>6937990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124986178</v>
+        <v>124981660</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587008</v>
+        <v>587048</v>
       </c>
       <c r="R4" t="n">
-        <v>6938211</v>
+        <v>6938056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982003</v>
+        <v>124988270</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587036</v>
+        <v>587190</v>
       </c>
       <c r="R5" t="n">
-        <v>6938128</v>
+        <v>6938036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124987318</v>
+        <v>124987424</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1159,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587102</v>
+        <v>587103</v>
       </c>
       <c r="R6" t="n">
-        <v>6938235</v>
+        <v>6938206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124983114</v>
+        <v>124986918</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91459</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586836</v>
+        <v>587054</v>
       </c>
       <c r="R7" t="n">
-        <v>6938079</v>
+        <v>6938245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124988969</v>
+        <v>124988050</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,39 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587225</v>
+        <v>587221</v>
       </c>
       <c r="R8" t="n">
-        <v>6937951</v>
+        <v>6938107</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124983267</v>
+        <v>124987817</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,14 +1520,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586804</v>
+        <v>587218</v>
       </c>
       <c r="R9" t="n">
-        <v>6938078</v>
+        <v>6938125</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124988529</v>
+        <v>124981850</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587145</v>
+        <v>587051</v>
       </c>
       <c r="R10" t="n">
-        <v>6938003</v>
+        <v>6938101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124983563</v>
+        <v>124982289</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586799</v>
+        <v>586956</v>
       </c>
       <c r="R11" t="n">
-        <v>6938055</v>
+        <v>6938114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,12 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124988323</v>
+        <v>124983114</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,39 +1846,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587174</v>
+        <v>586836</v>
       </c>
       <c r="R12" t="n">
-        <v>6938028</v>
+        <v>6938079</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,12 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124987125</v>
+        <v>124989520</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1977,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587084</v>
+        <v>587123</v>
       </c>
       <c r="R13" t="n">
-        <v>6938203</v>
+        <v>6937980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987817</v>
+        <v>124988914</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2070,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587218</v>
+        <v>587193</v>
       </c>
       <c r="R14" t="n">
-        <v>6938125</v>
+        <v>6937956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,22 +2164,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987740</v>
+        <v>124985568</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,34 +2192,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587191</v>
+        <v>587027</v>
       </c>
       <c r="R15" t="n">
-        <v>6938140</v>
+        <v>6938028</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2266,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,22 +2286,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124989520</v>
+        <v>124981815</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,38 +2310,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587123</v>
+        <v>587032</v>
       </c>
       <c r="R16" t="n">
-        <v>6937980</v>
+        <v>6938083</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124986538</v>
+        <v>124987125</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,14 +2450,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587003</v>
+        <v>587084</v>
       </c>
       <c r="R17" t="n">
-        <v>6938235</v>
+        <v>6938203</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2460,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,22 +2514,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988914</v>
+        <v>124988969</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,7 +2562,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2542,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587193</v>
+        <v>587225</v>
       </c>
       <c r="R18" t="n">
-        <v>6937956</v>
+        <v>6937951</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2607,22 +2636,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124981283</v>
+        <v>124989553</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,31 +2660,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2664,10 +2697,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587053</v>
+        <v>587128</v>
       </c>
       <c r="R19" t="n">
-        <v>6938038</v>
+        <v>6937990</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2732,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2742,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,22 +2757,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124982567</v>
+        <v>124982748</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2757,21 +2785,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2781,10 +2809,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586907</v>
+        <v>586911</v>
       </c>
       <c r="R20" t="n">
-        <v>6938087</v>
+        <v>6938088</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2826,7 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,10 +2881,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124982748</v>
+        <v>124987740</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,34 +2897,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586911</v>
+        <v>587191</v>
       </c>
       <c r="R21" t="n">
-        <v>6938088</v>
+        <v>6938140</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,7 +2956,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2938,7 +2966,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124988491</v>
+        <v>124985796</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,47 +3005,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587193</v>
+        <v>587080</v>
       </c>
       <c r="R22" t="n">
-        <v>6938003</v>
+        <v>6938107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3068,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3078,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,22 +3093,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124989553</v>
+        <v>124982003</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,47 +3117,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587128</v>
+        <v>587036</v>
       </c>
       <c r="R23" t="n">
-        <v>6937990</v>
+        <v>6938128</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3180,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3195,22 +3205,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124988185</v>
+        <v>124984652</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3243,14 +3253,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587197</v>
+        <v>586891</v>
       </c>
       <c r="R24" t="n">
-        <v>6938055</v>
+        <v>6937995</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3282,7 +3292,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,7 +3302,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3319,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124988050</v>
+        <v>124983267</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3355,14 +3365,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587221</v>
+        <v>586804</v>
       </c>
       <c r="R25" t="n">
-        <v>6938107</v>
+        <v>6938078</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3404,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3414,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,22 +3429,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124982170</v>
+        <v>124988185</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3447,39 +3457,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586964</v>
+        <v>587197</v>
       </c>
       <c r="R26" t="n">
-        <v>6938109</v>
+        <v>6938055</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3511,7 +3516,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3521,12 +3526,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3541,22 +3541,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124990166</v>
+        <v>124988323</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,35 +3565,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3602,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587097</v>
+        <v>587174</v>
       </c>
       <c r="R27" t="n">
-        <v>6937989</v>
+        <v>6938028</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3637,7 +3633,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3647,7 +3643,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3662,22 +3663,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124988270</v>
+        <v>124988415</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3714,10 +3715,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587190</v>
+        <v>587161</v>
       </c>
       <c r="R28" t="n">
-        <v>6938036</v>
+        <v>6938018</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3749,7 +3750,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3759,7 +3760,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,10 +3787,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124987889</v>
+        <v>124988529</v>
       </c>
       <c r="B29" t="n">
-        <v>91457</v>
+        <v>78947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3798,25 +3799,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3826,10 +3827,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587214</v>
+        <v>587145</v>
       </c>
       <c r="R29" t="n">
-        <v>6938134</v>
+        <v>6938003</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3861,7 +3862,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3871,7 +3872,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3886,22 +3887,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124987383</v>
+        <v>124987318</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3938,10 +3939,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587108</v>
+        <v>587102</v>
       </c>
       <c r="R30" t="n">
-        <v>6938215</v>
+        <v>6938235</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3973,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3983,7 +3984,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4011,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124986503</v>
+        <v>124983563</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4044,14 +4045,9 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4060,13 +4056,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587003</v>
+        <v>586799</v>
       </c>
       <c r="R31" t="n">
-        <v>6938230</v>
+        <v>6938055</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4095,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4105,7 +4101,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4120,22 +4121,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124981815</v>
+        <v>124981684</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4167,7 +4168,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4176,10 +4177,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587032</v>
+        <v>587057</v>
       </c>
       <c r="R32" t="n">
-        <v>6938083</v>
+        <v>6938054</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4211,7 +4212,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4221,7 +4222,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4248,10 +4249,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124981850</v>
+        <v>124988491</v>
       </c>
       <c r="B33" t="n">
-        <v>98122</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4260,38 +4261,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587051</v>
+        <v>587193</v>
       </c>
       <c r="R33" t="n">
-        <v>6938101</v>
+        <v>6938003</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4323,7 +4333,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4333,7 +4343,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4348,22 +4358,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124987424</v>
+        <v>124983653</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4376,16 +4386,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4401,14 +4411,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587103</v>
+        <v>586814</v>
       </c>
       <c r="R34" t="n">
-        <v>6938206</v>
+        <v>6938043</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4440,7 +4450,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4450,7 +4460,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4477,10 +4492,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124985931</v>
+        <v>124981403</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4513,7 +4528,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4522,10 +4537,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587058</v>
+        <v>587070</v>
       </c>
       <c r="R35" t="n">
-        <v>6938138</v>
+        <v>6938040</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4557,7 +4572,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4567,7 +4582,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4587,22 +4602,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124981660</v>
+        <v>124985931</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4615,34 +4630,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587048</v>
+        <v>587058</v>
       </c>
       <c r="R36" t="n">
-        <v>6938056</v>
+        <v>6938138</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4674,7 +4694,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4684,7 +4704,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4711,10 +4736,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124985568</v>
+        <v>124987521</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4727,39 +4752,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587027</v>
+        <v>587127</v>
       </c>
       <c r="R37" t="n">
-        <v>6938028</v>
+        <v>6938166</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4791,7 +4811,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,12 +4821,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,22 +4836,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124982289</v>
+        <v>124982567</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91459</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4849,39 +4864,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586956</v>
+        <v>586907</v>
       </c>
       <c r="R38" t="n">
-        <v>6938114</v>
+        <v>6938087</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4913,7 +4923,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4923,12 +4933,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4943,22 +4948,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124981403</v>
+        <v>124989421</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4971,39 +4976,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587070</v>
+        <v>587147</v>
       </c>
       <c r="R39" t="n">
-        <v>6938040</v>
+        <v>6937978</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5045,12 +5045,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5065,22 +5060,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124988918</v>
+        <v>124986178</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5093,39 +5088,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587221</v>
+        <v>587008</v>
       </c>
       <c r="R40" t="n">
-        <v>6937950</v>
+        <v>6938211</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5157,7 +5147,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5167,12 +5157,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5184,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124989421</v>
+        <v>124986503</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5215,37 +5200,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587147</v>
+        <v>587003</v>
       </c>
       <c r="R41" t="n">
-        <v>6937978</v>
+        <v>6938230</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5274,7 +5269,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,7 +5279,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5299,22 +5294,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124988415</v>
+        <v>124988918</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5327,34 +5322,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587161</v>
+        <v>587221</v>
       </c>
       <c r="R42" t="n">
-        <v>6938018</v>
+        <v>6937950</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5396,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,10 +5428,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124987066</v>
+        <v>124987889</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>91617</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5435,25 +5440,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5463,10 +5468,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587081</v>
+        <v>587214</v>
       </c>
       <c r="R43" t="n">
-        <v>6938219</v>
+        <v>6938134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5498,7 +5503,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5508,7 +5513,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5535,10 +5540,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124982589</v>
+        <v>124981283</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5551,34 +5556,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586904</v>
+        <v>587053</v>
       </c>
       <c r="R44" t="n">
-        <v>6938096</v>
+        <v>6938038</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5610,7 +5620,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5620,7 +5630,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5635,22 +5650,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124986659</v>
+        <v>124982170</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5663,34 +5678,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587032</v>
+        <v>586964</v>
       </c>
       <c r="R45" t="n">
-        <v>6938236</v>
+        <v>6938109</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5722,7 +5742,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5732,7 +5752,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5747,22 +5772,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124981756</v>
+        <v>124986538</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5775,42 +5800,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587045</v>
+        <v>587003</v>
       </c>
       <c r="R46" t="n">
-        <v>6938068</v>
+        <v>6938235</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5839,7 +5859,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5849,12 +5869,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5881,10 +5896,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124985796</v>
+        <v>124987383</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5921,10 +5936,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587080</v>
+        <v>587108</v>
       </c>
       <c r="R47" t="n">
-        <v>6938107</v>
+        <v>6938215</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5956,7 +5971,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5966,7 +5981,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5993,10 +6008,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124988641</v>
+        <v>124987066</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6009,39 +6024,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587123</v>
+        <v>587081</v>
       </c>
       <c r="R48" t="n">
-        <v>6937990</v>
+        <v>6938219</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6073,7 +6083,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6083,12 +6093,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6103,22 +6108,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124981684</v>
+        <v>124982589</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6127,42 +6132,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587057</v>
+        <v>586904</v>
       </c>
       <c r="R49" t="n">
-        <v>6938054</v>
+        <v>6938096</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6194,7 +6195,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +6205,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6219,22 +6220,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124984652</v>
+        <v>124981756</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6247,37 +6248,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586891</v>
+        <v>587045</v>
       </c>
       <c r="R50" t="n">
-        <v>6937995</v>
+        <v>6938068</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6306,7 +6312,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6316,7 +6322,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6331,22 +6342,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124982787</v>
+        <v>124986659</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6359,39 +6370,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>586882</v>
+        <v>587032</v>
       </c>
       <c r="R51" t="n">
-        <v>6938074</v>
+        <v>6938236</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6423,7 +6429,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6433,12 +6439,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6453,22 +6454,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124983653</v>
+        <v>124990166</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6477,43 +6478,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>586814</v>
+        <v>587097</v>
       </c>
       <c r="R52" t="n">
-        <v>6938043</v>
+        <v>6937989</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6545,7 +6550,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6555,12 +6560,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -6120,10 +6120,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124982589</v>
+        <v>124981756</v>
       </c>
       <c r="B49" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6136,37 +6136,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586904</v>
+        <v>587045</v>
       </c>
       <c r="R49" t="n">
-        <v>6938096</v>
+        <v>6938068</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6195,7 +6200,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6205,7 +6210,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6232,10 +6242,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124981756</v>
+        <v>124982589</v>
       </c>
       <c r="B50" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6248,42 +6258,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>587045</v>
+        <v>586904</v>
       </c>
       <c r="R50" t="n">
-        <v>6938068</v>
+        <v>6938096</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6312,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6322,12 +6327,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124982787</v>
+        <v>124981756</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -716,17 +716,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586882</v>
+        <v>587045</v>
       </c>
       <c r="R2" t="n">
-        <v>6938074</v>
+        <v>6938068</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124988641</v>
+        <v>124982589</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587123</v>
+        <v>586904</v>
       </c>
       <c r="R3" t="n">
-        <v>6937990</v>
+        <v>6938096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981660</v>
+        <v>124988185</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -959,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587048</v>
+        <v>587197</v>
       </c>
       <c r="R4" t="n">
-        <v>6938056</v>
+        <v>6938055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988270</v>
+        <v>124987889</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>91617</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587190</v>
+        <v>587214</v>
       </c>
       <c r="R5" t="n">
-        <v>6938036</v>
+        <v>6938134</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124987424</v>
+        <v>124985568</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,14 +1174,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587103</v>
+        <v>587027</v>
       </c>
       <c r="R6" t="n">
-        <v>6938206</v>
+        <v>6938028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124986918</v>
+        <v>124982170</v>
       </c>
       <c r="B7" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1271,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587054</v>
+        <v>586964</v>
       </c>
       <c r="R7" t="n">
-        <v>6938245</v>
+        <v>6938109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,19 +1365,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124988050</v>
+        <v>124984652</v>
       </c>
       <c r="B8" t="n">
         <v>78947</v>
@@ -1408,14 +1413,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587221</v>
+        <v>586891</v>
       </c>
       <c r="R8" t="n">
-        <v>6938107</v>
+        <v>6937995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987817</v>
+        <v>124981660</v>
       </c>
       <c r="B9" t="n">
         <v>78947</v>
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587218</v>
+        <v>587048</v>
       </c>
       <c r="R9" t="n">
-        <v>6938125</v>
+        <v>6938056</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124981850</v>
+        <v>124988918</v>
       </c>
       <c r="B10" t="n">
-        <v>98290</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1613,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587051</v>
+        <v>587221</v>
       </c>
       <c r="R10" t="n">
-        <v>6938101</v>
+        <v>6937950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124982289</v>
+        <v>124981815</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,43 +1735,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586956</v>
+        <v>587032</v>
       </c>
       <c r="R11" t="n">
-        <v>6938114</v>
+        <v>6938083</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,12 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,19 +1827,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124983114</v>
+        <v>124982748</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1870,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586836</v>
+        <v>586911</v>
       </c>
       <c r="R12" t="n">
-        <v>6938079</v>
+        <v>6938088</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,7 +1951,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124989520</v>
+        <v>124988050</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
@@ -1982,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587123</v>
+        <v>587221</v>
       </c>
       <c r="R13" t="n">
-        <v>6937980</v>
+        <v>6938107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988914</v>
+        <v>124987817</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,39 +2079,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587193</v>
+        <v>587218</v>
       </c>
       <c r="R14" t="n">
-        <v>6937956</v>
+        <v>6938125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2163,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124985568</v>
+        <v>124983267</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,39 +2191,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587027</v>
+        <v>586804</v>
       </c>
       <c r="R15" t="n">
-        <v>6938028</v>
+        <v>6938078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2250,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,12 +2260,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124981815</v>
+        <v>124982289</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,42 +2299,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587032</v>
+        <v>586956</v>
       </c>
       <c r="R16" t="n">
-        <v>6938083</v>
+        <v>6938114</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2377,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,22 +2397,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124987125</v>
+        <v>124982567</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,34 +2425,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587084</v>
+        <v>586907</v>
       </c>
       <c r="R17" t="n">
-        <v>6938203</v>
+        <v>6938087</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988969</v>
+        <v>124988529</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,39 +2537,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587225</v>
+        <v>587145</v>
       </c>
       <c r="R18" t="n">
-        <v>6937951</v>
+        <v>6938003</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,12 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124989553</v>
+        <v>124988323</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,35 +2645,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2697,10 +2678,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587128</v>
+        <v>587174</v>
       </c>
       <c r="R19" t="n">
-        <v>6937990</v>
+        <v>6938028</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2732,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2742,7 +2723,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,19 +2743,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124982748</v>
+        <v>124988270</v>
       </c>
       <c r="B20" t="n">
         <v>78947</v>
@@ -2805,14 +2791,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586911</v>
+        <v>587190</v>
       </c>
       <c r="R20" t="n">
-        <v>6938088</v>
+        <v>6938036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2854,7 +2840,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2881,7 +2867,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124987740</v>
+        <v>124987066</v>
       </c>
       <c r="B21" t="n">
         <v>80028</v>
@@ -2921,10 +2907,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587191</v>
+        <v>587081</v>
       </c>
       <c r="R21" t="n">
-        <v>6938140</v>
+        <v>6938219</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2966,7 +2952,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2981,22 +2967,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124985796</v>
+        <v>124987424</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,34 +2995,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587080</v>
+        <v>587103</v>
       </c>
       <c r="R22" t="n">
-        <v>6938107</v>
+        <v>6938206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3078,7 +3069,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3093,22 +3084,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124982003</v>
+        <v>124983563</v>
       </c>
       <c r="B23" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,34 +3112,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587036</v>
+        <v>586799</v>
       </c>
       <c r="R23" t="n">
-        <v>6938128</v>
+        <v>6938055</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3186,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,10 +3218,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124984652</v>
+        <v>124986538</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3233,34 +3234,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586891</v>
+        <v>587003</v>
       </c>
       <c r="R24" t="n">
-        <v>6937995</v>
+        <v>6938235</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3292,7 +3293,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3302,7 +3303,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3317,19 +3318,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124983267</v>
+        <v>124988415</v>
       </c>
       <c r="B25" t="n">
         <v>78947</v>
@@ -3365,14 +3366,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586804</v>
+        <v>587161</v>
       </c>
       <c r="R25" t="n">
-        <v>6938078</v>
+        <v>6938018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3404,7 +3405,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3414,7 +3415,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3429,22 +3430,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124988185</v>
+        <v>124987125</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3457,21 +3458,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3481,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587197</v>
+        <v>587084</v>
       </c>
       <c r="R26" t="n">
-        <v>6938055</v>
+        <v>6938203</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3526,7 +3527,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124988323</v>
+        <v>124989421</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,39 +3570,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587174</v>
+        <v>587147</v>
       </c>
       <c r="R27" t="n">
-        <v>6938028</v>
+        <v>6937978</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,7 +3629,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3643,12 +3639,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,10 +3666,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124988415</v>
+        <v>124988914</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3691,34 +3682,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587161</v>
+        <v>587193</v>
       </c>
       <c r="R28" t="n">
-        <v>6938018</v>
+        <v>6937956</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3750,7 +3746,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3760,7 +3756,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3775,22 +3776,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124988529</v>
+        <v>124987318</v>
       </c>
       <c r="B29" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3803,21 +3804,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3827,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587145</v>
+        <v>587102</v>
       </c>
       <c r="R29" t="n">
-        <v>6938003</v>
+        <v>6938235</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3862,7 +3863,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3872,7 +3873,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3899,10 +3900,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124987318</v>
+        <v>124981850</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
+        <v>98290</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,25 +3912,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3939,10 +3940,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587102</v>
+        <v>587051</v>
       </c>
       <c r="R30" t="n">
-        <v>6938235</v>
+        <v>6938101</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,7 +3975,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3984,7 +3985,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4011,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124983563</v>
+        <v>124986659</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4027,39 +4028,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586799</v>
+        <v>587032</v>
       </c>
       <c r="R31" t="n">
-        <v>6938055</v>
+        <v>6938236</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4087,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,12 +4097,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4133,10 +4124,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124981684</v>
+        <v>124989520</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,42 +4136,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587057</v>
+        <v>587123</v>
       </c>
       <c r="R32" t="n">
-        <v>6938054</v>
+        <v>6937980</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4212,7 +4199,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4222,7 +4209,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4249,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124988491</v>
+        <v>124987521</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4261,47 +4248,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587193</v>
+        <v>587127</v>
       </c>
       <c r="R33" t="n">
-        <v>6938003</v>
+        <v>6938166</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4333,7 +4311,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4343,7 +4321,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4358,19 +4336,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124983653</v>
+        <v>124988969</v>
       </c>
       <c r="B34" t="n">
         <v>57635</v>
@@ -4406,19 +4384,19 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586814</v>
+        <v>587225</v>
       </c>
       <c r="R34" t="n">
-        <v>6938043</v>
+        <v>6937951</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4450,7 +4428,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4460,7 +4438,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4480,19 +4458,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124981403</v>
+        <v>124988641</v>
       </c>
       <c r="B35" t="n">
         <v>57635</v>
@@ -4537,10 +4515,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587070</v>
+        <v>587123</v>
       </c>
       <c r="R35" t="n">
-        <v>6938040</v>
+        <v>6937990</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4572,7 +4550,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4582,7 +4560,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4602,19 +4580,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124985931</v>
+        <v>124981283</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
@@ -4650,7 +4628,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4659,10 +4637,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587058</v>
+        <v>587053</v>
       </c>
       <c r="R36" t="n">
-        <v>6938138</v>
+        <v>6938038</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4694,7 +4672,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4704,7 +4682,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4736,10 +4714,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124987521</v>
+        <v>124981684</v>
       </c>
       <c r="B37" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4748,38 +4726,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587127</v>
+        <v>587057</v>
       </c>
       <c r="R37" t="n">
-        <v>6938166</v>
+        <v>6938054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4811,7 +4793,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4821,7 +4803,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4848,10 +4830,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124982567</v>
+        <v>124987383</v>
       </c>
       <c r="B38" t="n">
-        <v>91459</v>
+        <v>80028</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4864,34 +4846,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586907</v>
+        <v>587108</v>
       </c>
       <c r="R38" t="n">
-        <v>6938087</v>
+        <v>6938215</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4923,7 +4905,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4933,7 +4915,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4960,10 +4942,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124989421</v>
+        <v>124982787</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4976,34 +4958,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587147</v>
+        <v>586882</v>
       </c>
       <c r="R39" t="n">
-        <v>6937978</v>
+        <v>6938074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5035,7 +5022,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5045,7 +5032,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5060,22 +5052,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124986178</v>
+        <v>124985931</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5088,34 +5080,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587008</v>
+        <v>587058</v>
       </c>
       <c r="R40" t="n">
-        <v>6938211</v>
+        <v>6938138</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5147,7 +5144,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5157,7 +5154,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5184,10 +5186,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124986503</v>
+        <v>124983114</v>
       </c>
       <c r="B41" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5200,47 +5202,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587003</v>
+        <v>586836</v>
       </c>
       <c r="R41" t="n">
-        <v>6938230</v>
+        <v>6938079</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5269,7 +5261,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5279,7 +5271,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5294,22 +5286,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124988918</v>
+        <v>124987740</v>
       </c>
       <c r="B42" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5322,39 +5314,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587221</v>
+        <v>587191</v>
       </c>
       <c r="R42" t="n">
-        <v>6937950</v>
+        <v>6938140</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5373,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,12 +5383,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5428,10 +5410,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124987889</v>
+        <v>124985796</v>
       </c>
       <c r="B43" t="n">
-        <v>91617</v>
+        <v>80028</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5440,25 +5422,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5468,10 +5450,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587214</v>
+        <v>587080</v>
       </c>
       <c r="R43" t="n">
-        <v>6938134</v>
+        <v>6938107</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5503,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5513,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,22 +5510,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124981283</v>
+        <v>124986918</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>91459</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5556,39 +5538,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587053</v>
+        <v>587054</v>
       </c>
       <c r="R44" t="n">
-        <v>6938038</v>
+        <v>6938245</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5620,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5630,12 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5662,10 +5634,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124982170</v>
+        <v>124990166</v>
       </c>
       <c r="B45" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5674,43 +5646,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586964</v>
+        <v>587097</v>
       </c>
       <c r="R45" t="n">
-        <v>6938109</v>
+        <v>6937989</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5742,7 +5718,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5752,12 +5728,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5784,10 +5755,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124986538</v>
+        <v>124988491</v>
       </c>
       <c r="B46" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5796,38 +5767,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587003</v>
+        <v>587193</v>
       </c>
       <c r="R46" t="n">
-        <v>6938235</v>
+        <v>6938003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5859,7 +5839,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5869,7 +5849,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5896,10 +5876,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124987383</v>
+        <v>124989553</v>
       </c>
       <c r="B47" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5908,38 +5888,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587108</v>
+        <v>587128</v>
       </c>
       <c r="R47" t="n">
-        <v>6938215</v>
+        <v>6937990</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5971,7 +5960,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5981,7 +5970,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5996,19 +5985,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124987066</v>
+        <v>124982003</v>
       </c>
       <c r="B48" t="n">
         <v>80028</v>
@@ -6048,10 +6037,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587081</v>
+        <v>587036</v>
       </c>
       <c r="R48" t="n">
-        <v>6938219</v>
+        <v>6938128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6083,7 +6072,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6093,7 +6082,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6108,19 +6097,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124981756</v>
+        <v>124986503</v>
       </c>
       <c r="B49" t="n">
         <v>57635</v>
@@ -6154,24 +6143,29 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587045</v>
+        <v>587003</v>
       </c>
       <c r="R49" t="n">
-        <v>6938068</v>
+        <v>6938230</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6200,7 +6194,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6210,12 +6204,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6242,10 +6231,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124982589</v>
+        <v>124983653</v>
       </c>
       <c r="B50" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6258,34 +6247,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586904</v>
+        <v>586814</v>
       </c>
       <c r="R50" t="n">
-        <v>6938096</v>
+        <v>6938043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6317,7 +6311,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6327,7 +6321,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6354,10 +6353,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124986659</v>
+        <v>124986178</v>
       </c>
       <c r="B51" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6370,21 +6369,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6394,10 +6393,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587032</v>
+        <v>587008</v>
       </c>
       <c r="R51" t="n">
-        <v>6938236</v>
+        <v>6938211</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6429,7 +6428,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6439,7 +6438,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6466,10 +6465,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124990166</v>
+        <v>124981403</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6478,35 +6477,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6515,10 +6510,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587097</v>
+        <v>587070</v>
       </c>
       <c r="R52" t="n">
-        <v>6937989</v>
+        <v>6938040</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6550,7 +6545,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6560,7 +6555,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981756</v>
+        <v>124982589</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587045</v>
+        <v>586904</v>
       </c>
       <c r="R2" t="n">
-        <v>6938068</v>
+        <v>6938096</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124982589</v>
+        <v>124981756</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586904</v>
+        <v>587045</v>
       </c>
       <c r="R3" t="n">
-        <v>6938096</v>
+        <v>6938068</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -3900,10 +3900,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124981850</v>
+        <v>124986659</v>
       </c>
       <c r="B30" t="n">
-        <v>98290</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3912,25 +3912,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587051</v>
+        <v>587032</v>
       </c>
       <c r="R30" t="n">
-        <v>6938101</v>
+        <v>6938236</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124986659</v>
+        <v>124989520</v>
       </c>
       <c r="B31" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587032</v>
+        <v>587123</v>
       </c>
       <c r="R31" t="n">
-        <v>6938236</v>
+        <v>6937980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4124,10 +4124,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124989520</v>
+        <v>124987521</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587123</v>
+        <v>587127</v>
       </c>
       <c r="R32" t="n">
-        <v>6937980</v>
+        <v>6938166</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124987521</v>
+        <v>124981850</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
+        <v>98290</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4248,25 +4248,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587127</v>
+        <v>587051</v>
       </c>
       <c r="R33" t="n">
-        <v>6938166</v>
+        <v>6938101</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5876,10 +5876,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124989553</v>
+        <v>124982003</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5888,47 +5888,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587128</v>
+        <v>587036</v>
       </c>
       <c r="R47" t="n">
-        <v>6937990</v>
+        <v>6938128</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5960,7 +5951,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5970,7 +5961,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5985,22 +5976,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124982003</v>
+        <v>124989553</v>
       </c>
       <c r="B48" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6009,38 +6000,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587036</v>
+        <v>587128</v>
       </c>
       <c r="R48" t="n">
-        <v>6938128</v>
+        <v>6937990</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6097,12 +6097,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124982589</v>
+        <v>124981756</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586904</v>
+        <v>587045</v>
       </c>
       <c r="R2" t="n">
-        <v>6938096</v>
+        <v>6938068</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981756</v>
+        <v>124982589</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +813,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587045</v>
+        <v>586904</v>
       </c>
       <c r="R3" t="n">
-        <v>6938068</v>
+        <v>6938096</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981756</v>
+        <v>124987383</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587045</v>
+        <v>587108</v>
       </c>
       <c r="R2" t="n">
-        <v>6938068</v>
+        <v>6938215</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124982589</v>
+        <v>124988415</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586904</v>
+        <v>587161</v>
       </c>
       <c r="R3" t="n">
-        <v>6938096</v>
+        <v>6938018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124988185</v>
+        <v>124982003</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587197</v>
+        <v>587036</v>
       </c>
       <c r="R4" t="n">
-        <v>6938055</v>
+        <v>6938128</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,50 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987889</v>
+        <v>124988918</v>
       </c>
       <c r="B5" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587214</v>
+        <v>587221</v>
       </c>
       <c r="R5" t="n">
-        <v>6938134</v>
+        <v>6937950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,27 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124985568</v>
+        <v>124988270</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587027</v>
+        <v>587190</v>
       </c>
       <c r="R6" t="n">
-        <v>6938028</v>
+        <v>6938036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, märkt med vägsnitsel</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,27 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124982170</v>
+        <v>124988185</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,39 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586964</v>
+        <v>587197</v>
       </c>
       <c r="R7" t="n">
-        <v>6938109</v>
+        <v>6938055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,62 +1315,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124984652</v>
+        <v>124989553</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586891</v>
+        <v>587128</v>
       </c>
       <c r="R8" t="n">
-        <v>6937995</v>
+        <v>6937990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,27 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124981660</v>
+        <v>124986659</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587048</v>
+        <v>587032</v>
       </c>
       <c r="R9" t="n">
-        <v>6938056</v>
+        <v>6938236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,16 +1550,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124988918</v>
+        <v>124988641</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1646,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587221</v>
+        <v>587123</v>
       </c>
       <c r="R10" t="n">
-        <v>6937950</v>
+        <v>6937990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1635,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1723,54 +1667,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124981815</v>
+        <v>124982289</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587032</v>
+        <v>586956</v>
       </c>
       <c r="R11" t="n">
-        <v>6938083</v>
+        <v>6938114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1752,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,27 +1772,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124982748</v>
+        <v>124988969</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,34 +1795,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586911</v>
+        <v>587225</v>
       </c>
       <c r="R12" t="n">
-        <v>6938088</v>
+        <v>6937951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1869,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,37 +1901,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124988050</v>
+        <v>124987889</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587221</v>
+        <v>587214</v>
       </c>
       <c r="R13" t="n">
-        <v>6938107</v>
+        <v>6938134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +1971,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +1981,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,28 +1996,23 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987817</v>
+        <v>124982748</v>
       </c>
       <c r="B14" t="n">
         <v>78947</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2099,14 +2039,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587218</v>
+        <v>586911</v>
       </c>
       <c r="R14" t="n">
-        <v>6938125</v>
+        <v>6938088</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,50 +2115,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124983267</v>
+        <v>124988491</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586804</v>
+        <v>587193</v>
       </c>
       <c r="R15" t="n">
-        <v>6938078</v>
+        <v>6938003</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,15 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124982289</v>
+        <v>124983114</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,39 +2242,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586956</v>
+        <v>586836</v>
       </c>
       <c r="R16" t="n">
-        <v>6938114</v>
+        <v>6938079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2301,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,12 +2311,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska och äldre</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,27 +2326,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124982567</v>
+        <v>124982170</v>
       </c>
       <c r="B17" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,34 +2349,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586907</v>
+        <v>586964</v>
       </c>
       <c r="R17" t="n">
-        <v>6938087</v>
+        <v>6938109</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2423,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,27 +2443,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988529</v>
+        <v>124985796</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,21 +2466,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2561,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587145</v>
+        <v>587080</v>
       </c>
       <c r="R18" t="n">
-        <v>6938003</v>
+        <v>6938107</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2535,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,16 +2562,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124988323</v>
+        <v>124986503</v>
       </c>
       <c r="B19" t="n">
         <v>57635</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2667,24 +2591,29 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587174</v>
+        <v>587003</v>
       </c>
       <c r="R19" t="n">
-        <v>6938028</v>
+        <v>6938230</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2713,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,12 +2652,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,27 +2667,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124988270</v>
+        <v>124983563</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2771,34 +2690,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587190</v>
+        <v>586799</v>
       </c>
       <c r="R20" t="n">
-        <v>6938036</v>
+        <v>6938055</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2754,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2764,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,15 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124987066</v>
+        <v>124981403</v>
       </c>
       <c r="B21" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,34 +2807,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587081</v>
+        <v>587070</v>
       </c>
       <c r="R21" t="n">
-        <v>6938219</v>
+        <v>6938040</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2871,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,7 +2881,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,15 +2913,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124987424</v>
+        <v>124982589</v>
       </c>
       <c r="B22" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,39 +2924,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587103</v>
+        <v>586904</v>
       </c>
       <c r="R22" t="n">
-        <v>6938206</v>
+        <v>6938096</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +2983,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,7 +2993,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,15 +3020,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124983563</v>
+        <v>124986538</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,39 +3031,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586799</v>
+        <v>587003</v>
       </c>
       <c r="R23" t="n">
-        <v>6938055</v>
+        <v>6938235</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,7 +3090,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,12 +3100,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,27 +3115,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124986538</v>
+        <v>124985568</v>
       </c>
       <c r="B24" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,34 +3138,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587003</v>
+        <v>587027</v>
       </c>
       <c r="R24" t="n">
-        <v>6938235</v>
+        <v>6938028</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3293,7 +3202,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3303,7 +3212,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, märkt med vägsnitsel</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,15 +3244,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124988415</v>
+        <v>124981283</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,34 +3255,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587161</v>
+        <v>587053</v>
       </c>
       <c r="R25" t="n">
-        <v>6938018</v>
+        <v>6938038</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3405,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3415,7 +3329,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,50 +3361,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124987125</v>
+        <v>124981815</v>
       </c>
       <c r="B26" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587084</v>
+        <v>587032</v>
       </c>
       <c r="R26" t="n">
-        <v>6938203</v>
+        <v>6938083</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,7 +3435,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,7 +3445,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,15 +3472,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124989421</v>
+        <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3570,34 +3483,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587147</v>
+        <v>587103</v>
       </c>
       <c r="R27" t="n">
-        <v>6937978</v>
+        <v>6938206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,7 +3547,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3639,7 +3557,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3654,12 +3572,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3671,11 +3589,6 @@
       <c r="B28" t="n">
         <v>57635</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3788,15 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124987318</v>
+        <v>124986918</v>
       </c>
       <c r="B29" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3804,21 +3712,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3828,10 +3736,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587102</v>
+        <v>587054</v>
       </c>
       <c r="R29" t="n">
-        <v>6938235</v>
+        <v>6938245</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3863,7 +3771,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3873,7 +3781,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,15 +3808,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124986659</v>
+        <v>124989421</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3940,10 +3843,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587032</v>
+        <v>587147</v>
       </c>
       <c r="R30" t="n">
-        <v>6938236</v>
+        <v>6937978</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,7 +3878,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +3888,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,15 +3915,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124989520</v>
+        <v>124983653</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4028,34 +3926,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587123</v>
+        <v>586814</v>
       </c>
       <c r="R31" t="n">
-        <v>6937980</v>
+        <v>6938043</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4087,7 +3990,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4097,7 +4000,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4112,27 +4020,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124987521</v>
+        <v>124981756</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4140,37 +4043,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587127</v>
+        <v>587045</v>
       </c>
       <c r="R32" t="n">
-        <v>6938166</v>
+        <v>6938068</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4199,7 +4107,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4209,7 +4117,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4224,49 +4137,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124981850</v>
+        <v>124981660</v>
       </c>
       <c r="B33" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4276,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587051</v>
+        <v>587048</v>
       </c>
       <c r="R33" t="n">
-        <v>6938101</v>
+        <v>6938056</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4311,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4321,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4348,43 +4256,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124988969</v>
+        <v>124990166</v>
       </c>
       <c r="B34" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4393,10 +4300,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587225</v>
+        <v>587097</v>
       </c>
       <c r="R34" t="n">
-        <v>6937951</v>
+        <v>6937989</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4428,7 +4335,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4438,12 +4345,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:35</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4458,27 +4360,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124988641</v>
+        <v>124986178</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4486,39 +4383,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587123</v>
+        <v>587008</v>
       </c>
       <c r="R35" t="n">
-        <v>6937990</v>
+        <v>6938211</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4550,7 +4442,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4560,12 +4452,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4592,15 +4479,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124981283</v>
+        <v>124988050</v>
       </c>
       <c r="B36" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,39 +4490,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587053</v>
+        <v>587221</v>
       </c>
       <c r="R36" t="n">
-        <v>6938038</v>
+        <v>6938107</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4672,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4682,12 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4714,54 +4586,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124981684</v>
+        <v>124982567</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587057</v>
+        <v>586907</v>
       </c>
       <c r="R37" t="n">
-        <v>6938054</v>
+        <v>6938087</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4793,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4803,7 +4666,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4830,15 +4693,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124987383</v>
+        <v>124984652</v>
       </c>
       <c r="B38" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4846,34 +4704,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
+          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587108</v>
+        <v>586891</v>
       </c>
       <c r="R38" t="n">
-        <v>6938215</v>
+        <v>6937995</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4905,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4915,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4942,55 +4800,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124982787</v>
+        <v>124981850</v>
       </c>
       <c r="B39" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98290</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586882</v>
+        <v>587051</v>
       </c>
       <c r="R39" t="n">
-        <v>6938074</v>
+        <v>6938101</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5022,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5032,12 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5052,27 +4895,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124985931</v>
+        <v>124987521</v>
       </c>
       <c r="B40" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5080,39 +4918,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587058</v>
+        <v>587127</v>
       </c>
       <c r="R40" t="n">
-        <v>6938138</v>
+        <v>6938166</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5144,7 +4977,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5154,12 +4987,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:32</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5186,16 +5014,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124983114</v>
+        <v>124983267</v>
       </c>
       <c r="B41" t="n">
         <v>78947</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5226,10 +5049,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586836</v>
+        <v>586804</v>
       </c>
       <c r="R41" t="n">
-        <v>6938079</v>
+        <v>6938078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5261,7 +5084,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5271,7 +5094,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5286,27 +5109,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124987740</v>
+        <v>124987817</v>
       </c>
       <c r="B42" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5314,21 +5132,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5338,10 +5156,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587191</v>
+        <v>587218</v>
       </c>
       <c r="R42" t="n">
-        <v>6938140</v>
+        <v>6938125</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5373,7 +5191,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5383,7 +5201,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5410,50 +5228,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124985796</v>
+        <v>124981684</v>
       </c>
       <c r="B43" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587080</v>
+        <v>587057</v>
       </c>
       <c r="R43" t="n">
-        <v>6938107</v>
+        <v>6938054</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5485,7 +5302,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5495,7 +5312,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5522,15 +5339,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124986918</v>
+        <v>124988529</v>
       </c>
       <c r="B44" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5538,21 +5350,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5562,10 +5374,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587054</v>
+        <v>587145</v>
       </c>
       <c r="R44" t="n">
-        <v>6938245</v>
+        <v>6938003</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5409,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5419,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5634,59 +5446,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124990166</v>
+        <v>124987740</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587097</v>
+        <v>587191</v>
       </c>
       <c r="R45" t="n">
-        <v>6937989</v>
+        <v>6938140</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5718,7 +5516,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5728,7 +5526,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5743,71 +5541,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124988491</v>
+        <v>124987066</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>587193</v>
+        <v>587081</v>
       </c>
       <c r="R46" t="n">
-        <v>6938003</v>
+        <v>6938219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5839,7 +5623,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5849,7 +5633,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5876,15 +5660,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124982003</v>
+        <v>124985931</v>
       </c>
       <c r="B47" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5892,34 +5671,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>587036</v>
+        <v>587058</v>
       </c>
       <c r="R47" t="n">
-        <v>6938128</v>
+        <v>6938138</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5951,7 +5735,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5961,7 +5745,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5988,47 +5777,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124989553</v>
+        <v>124988323</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6037,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>587128</v>
+        <v>587174</v>
       </c>
       <c r="R48" t="n">
-        <v>6937990</v>
+        <v>6938028</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6072,7 +5852,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6082,7 +5862,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6097,27 +5882,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124986503</v>
+        <v>124987125</v>
       </c>
       <c r="B49" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6125,47 +5905,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kroktjärnmyran, Kroktjärnmyran, Mpd</t>
+          <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>587003</v>
+        <v>587084</v>
       </c>
       <c r="R49" t="n">
-        <v>6938230</v>
+        <v>6938203</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6194,7 +5964,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6204,7 +5974,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6219,28 +5989,23 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124983653</v>
+        <v>124982787</v>
       </c>
       <c r="B50" t="n">
         <v>57635</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6267,7 +6032,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6276,10 +6041,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586814</v>
+        <v>586882</v>
       </c>
       <c r="R50" t="n">
-        <v>6938043</v>
+        <v>6938074</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6311,7 +6076,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6321,7 +6086,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6353,16 +6118,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124986178</v>
+        <v>124989520</v>
       </c>
       <c r="B51" t="n">
         <v>78947</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6393,10 +6153,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>587008</v>
+        <v>587123</v>
       </c>
       <c r="R51" t="n">
-        <v>6938211</v>
+        <v>6937980</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6428,7 +6188,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6438,7 +6198,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6465,15 +6225,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124981403</v>
+        <v>124987318</v>
       </c>
       <c r="B52" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6481,39 +6236,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svanatjärnmyran, Svanatjärnmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>587070</v>
+        <v>587102</v>
       </c>
       <c r="R52" t="n">
-        <v>6938040</v>
+        <v>6938235</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6545,7 +6295,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6555,12 +6305,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6575,12 +6320,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -3475,7 +3475,7 @@
         <v>124987424</v>
       </c>
       <c r="B27" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>124988918</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>124988641</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>124982289</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>124988969</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>124982170</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>124983563</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>124981403</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>124985568</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>124981283</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>124988914</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>124983653</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>124981756</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>124985931</v>
       </c>
       <c r="B47" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>124988323</v>
       </c>
       <c r="B48" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>124982787</v>
       </c>
       <c r="B50" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>124988918</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>124988641</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>124982289</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>124988969</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>124982170</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>124983563</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>124981403</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>124985568</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>124981283</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>124988914</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>124983653</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>124981756</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>124985931</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>124988323</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>124982787</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">

--- a/artfynd/A 47177-2024 artfynd.xlsx
+++ b/artfynd/A 47177-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY153"/>
+  <dimension ref="A1:AZ153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446380</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446383</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446384</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446201</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446356</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982567</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986918</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446391</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982589</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446181</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446226</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446362</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446368</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446218</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987889</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124984531</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446189</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446190</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446212</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2923,6 +3028,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446230</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3030,6 +3140,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3137,6 +3252,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446198</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3244,6 +3364,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124981660</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3351,6 +3476,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982748</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3458,6 +3588,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983114</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3565,6 +3700,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983267</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3672,6 +3812,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124984652</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3779,6 +3924,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986178</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3886,6 +4036,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987817</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3993,6 +4148,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988050</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4100,6 +4260,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988185</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4207,6 +4372,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988270</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4314,6 +4484,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988415</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4421,6 +4596,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988529</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4528,6 +4708,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124989421</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4635,6 +4820,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124989520</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4742,6 +4932,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446177</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4849,6 +5044,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446197</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4956,6 +5156,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446199</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5063,6 +5268,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446202</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5170,6 +5380,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446217</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5277,6 +5492,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446234</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5384,6 +5604,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446235</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5491,6 +5716,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446355</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5598,6 +5828,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446375</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5705,6 +5940,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446178</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5812,6 +6052,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446188</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5919,6 +6164,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446195</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6026,6 +6276,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446208</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6133,6 +6388,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446211</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6240,6 +6500,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446213</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6347,6 +6612,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446222</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6454,6 +6724,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446224</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6561,6 +6836,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446225</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6668,6 +6948,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446227</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6775,6 +7060,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446228</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6882,6 +7172,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446231</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6989,6 +7284,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446366</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7096,6 +7396,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446372</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7203,6 +7508,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446373</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7310,6 +7620,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446374</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7417,6 +7732,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446382</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7524,6 +7844,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446386</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7631,6 +7956,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446387</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7738,6 +8068,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446390</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7845,6 +8180,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446232</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7952,6 +8292,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446223</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8059,6 +8404,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446233</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8166,6 +8516,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446179</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8273,6 +8628,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982003</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8380,6 +8740,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124984470</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8487,6 +8852,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124984955</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8594,6 +8964,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124985205</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8701,6 +9076,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124985796</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8808,6 +9188,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986538</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8915,6 +9300,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986659</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9022,6 +9412,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987066</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9129,6 +9524,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987125</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9236,6 +9636,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987318</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9343,6 +9748,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987383</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9450,6 +9860,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987521</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9557,6 +9972,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987740</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9664,6 +10084,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446180</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9771,6 +10196,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446184</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9878,6 +10308,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446191</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9985,6 +10420,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446204</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10092,6 +10532,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446205</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10204,6 +10649,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446206</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10311,6 +10761,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446214</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10418,6 +10873,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446216</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10525,6 +10985,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446365</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10632,6 +11097,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446370</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10739,6 +11209,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446388</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10846,6 +11321,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446182</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10953,6 +11433,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446183</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11060,6 +11545,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446185</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11167,6 +11657,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446187</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11274,6 +11769,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446192</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11381,6 +11881,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446193</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11488,6 +11993,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446196</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11595,6 +12105,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446203</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11702,6 +12217,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446207</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11809,6 +12329,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446215</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11916,6 +12441,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446369</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12023,6 +12553,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446389</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12130,6 +12665,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446221</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12237,6 +12777,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446220</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12349,6 +12894,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987424</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12466,6 +13016,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124981283</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12583,6 +13138,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124981403</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12700,6 +13260,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124981756</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12817,6 +13382,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982170</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12934,6 +13504,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982289</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13051,6 +13626,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982787</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13168,6 +13748,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983563</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13285,6 +13870,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124983653</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13402,6 +13992,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124984046</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13519,6 +14114,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124985568</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13636,6 +14236,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124985931</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13753,6 +14358,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986503</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13870,6 +14480,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988323</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13987,6 +14602,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988641</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14104,6 +14724,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988914</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14221,6 +14846,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988918</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14338,6 +14968,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988969</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14458,6 +15093,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446236</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14578,6 +15218,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446361</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14698,6 +15343,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446377</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14818,6 +15468,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446385</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14930,6 +15585,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446209</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15037,6 +15697,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446210</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15144,6 +15809,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446363</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15251,6 +15921,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446364</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15362,6 +16037,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124981684</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15473,6 +16153,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124981815</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15589,6 +16274,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124984686</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15705,6 +16395,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988491</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15821,6 +16516,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124989553</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15937,6 +16637,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124990166</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16049,6 +16754,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446357</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16161,6 +16871,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446358</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16273,6 +16988,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446360</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16380,6 +17100,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446378</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16487,6 +17212,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446371</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16594,6 +17324,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446376</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16701,6 +17436,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124981850</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16808,6 +17548,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446186</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16915,6 +17660,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446194</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17022,6 +17772,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446367</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17129,6 +17884,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446379</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17236,8 +17996,167 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446219</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>